--- a/data/worldcup_0627_0623update.xlsx
+++ b/data/worldcup_0627_0623update.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -452,6 +452,2401 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>摘要</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>两场比赛同开！法国vs伊拉克比赛恢复 挪威vs塞内加尔8点开球</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-06-23 08:06:37</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-23/6a39c984b4a8anative.htm</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>I组积分榜：法国力压挪威居首，末轮双方上演头名之争</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959295&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>France vs Iraq resumes after two-hour weather delay at the World Cup</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tue, 23 Jun 2026 00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/person/player/france-vs-iraq-resumes-after-two-hour-weather-delay-at-the-world-cup</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The World Cup 2026 match between France and Iraq in Group I has resumed after a weather break of around two hours and 15 minutes.  France vs Iraq was </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Norway v Senegal: World Cup 2026 – live</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tue Jun 23 2026 00:</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/live/2026/jun/22/norway-v-senegal-world-cup-2026-live</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>⚽️ World Cup kick-off: 8pm ET/1am BST/10am AEST ⚽️ Player guide | Bracketology | Golden Boot | Email Jeff  1 min They’re off and trotting in East Ruth</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>France v Iraq: match resumes after two-hour storm delay at World Cup 2026 – live</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Tue Jun 23 2026 00:</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/live/2026/jun/22/france-v-iraq-world-cup-2026-live-updates</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚽️ World Cup kick-off: 5pm ET/10pm BST/7am AEST ⚽️ Player guide | Bracketology | Golden Boot | Email Tim  46 min The game resumes! And it’s still 1-0 </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Golden Boot: World Cup 2026 top goalscorers</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Thu, 18 Jun 2026 08</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/ng-interactive/2026/jun/04/golden-boot-world-cup-2026-top-goalscorers-winner</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Who is winning the battle to be top scorer at the World Cup? Live and updated throughout the tournament  All-time World Cup goalscorers  The Golden Bo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Who is the referee for Uruguay vs Cape Verde?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 20</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/who-is-the-referee-for-uruguay-vs-cape-verde</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uruguay have a great chance to register their first World Cup 2026 win at the Hard Rock Stadium in Miami, where they face Cape Verde.  The latter may </t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>‘Our performance until that stage had clearly made Kylian Mbappe angry, and suddenly you saw this explosion’ Frank Leboeuf on France’s epic World Cup 2022 final defeat</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 15</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/person/player/our-performance-until-that-stage-had-clearly-made-kylian-mbappe-angry-and-suddenly-you-saw-this-explosion-frank-leboeuf-on-frances-epic-world-cup-2022-final-defeat</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>The 2022 World Cup final in Qatar was perhaps the most dramatic climax in the tournament’s storied history.  It was a match packed with momentum swing</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Guns for hire and gegenpress eggheads bring World Cup subplots aplenty</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 13</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/21/football-daily-geopolitics-world-cup-maverick-managerial-matchups</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>The awesome thing about a World Cup is that – unlike the Premier League where almost every elite-grade head coach comes from the same scenic Spanish t</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>The French aristocrat and the all-American idiot: Henry v Lalas is the World Cup’s most compelling battle</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 09</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/21/thierry-henry-alexi-lalas-fox-world-cup</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fox’s broadcast at the tournament has become a story of two contrasting styles. And there is one clear winner  W e all know someone like Alexi Lalas. </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>France vs Iraq plunged into weather chaos - what are the World Cup 2026 weather protocols?</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 22</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/france-vs-iraq-sees-weather-chaos-ensue-what-are-the-protocols</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>France vs Iraq is currently paused, with the former up 1-0 through a Kylian Mbappe and Michael Olise link-up in the 14th minute.  Mbappe , now just th</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>How to watch Norway vs Senegal for FREE: Live stream details for a crucial World Cup 2026 Group I</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 22</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/watch-norway-vs-senegal-free-world-cup-2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>It's always dangerous to assume anything about what lies ahead in a major tournament but Norway vs Senegal feels like Group I's decisive fixture at th</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Who is the referee for Norway vs Senegal?</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 22</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/who-is-the-referee-for-norway-vs-senegal</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Norway are set to face Senegal as World Cup's Group I reaches its second round of fixtures.  Norway are looking to build on their impressive 4-1 win o</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Norway vs Senegal prediction: Can Norway continue their fast World Cup start?</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 21</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/norway-vs-senegal-prediction-can-norway-continue-their-fast-world-cup-start</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Norway and Senegal go head-to-head tonight in what could be a thrilling match in Group I.  Erling Haaland impressed as the Norwegians got off to a str</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Who is the referee for France vs Iraq?</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 20</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/who-is-the-referee-for-france-vs-iraq</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>France lived up to their pre-tournament billing when they dispatched Senegal 3-1 in their opening Group I clash last week.  The spotlight had firmly b</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Mbappe World Cup goals: How many does the Frenchman need to overtake Lionel Messi?</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 19</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/person/player/mbappe-world-cup-goals-how-many-does-the-frenchman-need-to-overtake-lionel-messi</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Kylian Mbappe is on track to becoming the World Cup's greatest ever player, having made it to two successful finals with France at the tournament.  Th</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>How to watch France vs Iraq for FREE: Live stream details as Kylian Mbappe chases history at World Cup 2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 19</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/watch-france-vs-iraq-for-free-world-cup-2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Kylian Mbappe broke France's goalscoring record, on matchday one at the World Cup 2026 , and Les Bleus' skipper will be hungry for more as he leads hi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>France vs Iraq prediction: Will Kylian Mbappe add to his World Cup goal tally?</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/france-vs-iraq-prediction-will-kylian-mbappe-add-to-his-world-cup-goal-tally</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>You've got to feel for Iraq in Group I.  Graham Arnold's side are playing in their first World Cup for 40 years, but had to play second fiddle to Norw</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Quiz! Can you name every Frenchman to have played in a World Cup final?</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 07</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/quiz/football-quiz-can-you-name-every-frenchman-to-have-played-in-a-world-cup-final</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLAY NOW You can play all FourFourTwo quizzes right HERE  France are back in action, and as one of the world's great superpowers, they've sprung into </t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Squawka’s World Cup AI Predictor: AI score predictions for Monday June 22 at the 2026 World Cup</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>9 hours ago</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/squawkas-world-cup-ai-predictor-22-06/</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Using data from previous tournaments and qualifying, we’ve tasked our model with creating some World Cup AI predictions with correct score picks on ev</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>本届世界杯首次！RMC：法国vs伊拉克下半场补水暂停取消</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-06-23 08:06:37</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-23/6a39c8440f8e6native.htm</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>太阳报：法国世界杯冠军吉瓦尔什退役后销售泳池，不再与队友联系</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-06-23 08:06:37</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-23/6a39cbdba4eb3native.htm</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>世界杯-挪威vs塞内加尔首发：哈兰德PK马内！厄德高、杰克逊出战</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-06-23 06:35:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-23/6a396818a047dnative.htm</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>World Cup Daily: France-Iraq restarts after temporary suspension due to weather</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-06-22T23:51:26</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/soccer/story/_/id/49141065/world-cup-daily-crying-belgium-fan-saved-var-messi-mbappe-haaland-action</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>It's another week of 2026 FIFA World Cup action, and we have some big teams playing today, including Argentina, France and Norway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Doku returning to World Cup after birth of first child</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-06-22T10:01:15</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cly01kjqdnpo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jeremy Doku moved to Manchester City from Rennes in 2023 for Â£55.4m  Jeremy Doku has made it clear - family comes first.  The Manchester City winger </t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>How do you stop Messi, Mbappe, Haaland and Kane?</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-06-22T08:10:21</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cly8gpp39d0o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Four of the most in-form strikers in world football will look to add to their red-hot starts to the World Cup this week  A World Cup is always that li</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>队报预测法国vs伊拉克首发：姆总、奥利塞、登贝莱和巴尔科拉出战</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-06-22 17:50:15</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a3900c8421e4native.htm</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>官方：挪威vs伊拉克创97%收视率 是21世纪挪威世界杯赛事第2高</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-06-22 16:43:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a38f548707e8native.htm</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>6月22日世界杯看点：梅西雕像遭吐槽 阿根廷法国再登场</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-06-22 15:21:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a38e1f74a97anative.htm</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>6.22竞足看点：挪威将面对非洲劲敌；阿根廷、奥地利阵容不整</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:56</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5957008.html</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>伊拉克主帅：能和法国队交手是荣幸，也是我们展现实力的机会</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-06-22 06:53</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956272</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>伊拉克将在世界杯小组赛第二场对阵法国，主帅阿诺德赛前接受了拜因体育的采访。
+对伊拉克队来说，这是一段非常美妙的经历。能够与法国队这样的球队交手，是一种荣幸。我之前也公开表示过，我非常享受这一切。无论是对阵挪威，还是接下来的比赛，都是如此。我从中收获了很多快乐。
+会的。为了争取最好的结果，我们必须</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Slick Spain shine as Sharks shock the Celeste</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-06-21T22:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/matchday-11-round-up-review-highlights</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Lamine Yamal got Spain scoring at the FIFA World Cup 2026™ but it was Cabo Verde who once again stole the show with a 2-2 draw against Uruguay.
+Spain</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>The World Cup records that look set to be broken</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-06-21T13:55:05</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cpv3kkv4z4mo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Lionel Messi has appeared at six World Cups, scoring 16 goals  The 2026 World Cup may only be 10 days old but the tournament has already rewritten foo</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>France vs Iraq Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-06-21T09:26:39</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/france-vs-iraq-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Can Kylian Mbappé make history as he joins France’s centurions club? Look ahead to this Group I clash at the 2026 FIFA World Cup with our France vs Ir</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Norway vs Senegal Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-06-21T09:21:55</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/norway-vs-senegal-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>After getting off to contrasting starts in their respective FIFA World Cup openers, Norway and Senegal will meet in New York in what is sure to be a h</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Argentina and France among quartet eyeing knockout stage</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-06-21T09:00:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/preview-matchday-twelve</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Find out all the key details as Groups I and J return to action at FIFA World Cup 2026, headlined by former winners Argentina and France.
+Argentina m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>世界杯成移民球员最大舞台，99名法国出生者将为他国出战</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-06-21 18:02</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5954863.html</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>伊拉克VS挪威这是哈兰德的第一次世界杯，如果梅开...</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-06-21 16:59</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5940517.html</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>OptaJean：勒纳尔成法国第二位在世界杯执教3支国家队的教练</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-06-21 11:23</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5954280.html</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>The Four Major Storylines Fueling France’s World Cup 2026 Campaign</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-06-19T09:30:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/the-four-major-storylines-fueling-frances-world-cup-2026-campaign</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>From Mbappé’s off-pitch drama to Deschamps’ potential last dance, France arrive at the 2026 World Cup as favorites with plenty of storylines beyond th</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>官方：揭幕战主裁桑帕约将执法世界杯挪威vs塞内加尔</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-06-19 20:51</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5949666.html</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>France vs Iraq; FIFA World Cup Group I</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>skysports</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>10:00pm, Monday 22n</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.skysports.com/football/france-vs-iraq/report/549806</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>France                           vs Iraq. FIFA World Cup Group I.  10:00pm, Monday 22nd June 2026.  Philadelphia Stadium Attendance: Attendance 68,324</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>France vs Iraq: predictions, best bets, odds and stats</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1 hour ago</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/france-vs-iraq-predictions-tips-22-06-26/</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No previous meetings between these teams.
+No price boosts for this event.
+Bet Builder is not available yet.
+Betting markets are not available yet.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Norway vs Senegal: predictions, best bets, odds and stats</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1 hour ago</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/norway-vs-senegal-predictions-tips-23-06-26/</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No previous meetings between these teams.
+No price boosts for this event.
+Bet Builder is not available yet.
+Betting markets are not available yet.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>挪威首战平均观众130万，为本世纪挪威国内世界杯比赛第二高</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5957229&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Norway at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/norway-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>A team profile of Norway, back at the FIFA World Cup after 28 years: 32nd in the FIFA ranking, 4th appearance, Stale Solbakken's tactics, stars Erling</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>墨美德阿之后第五支，法国队两连胜晋级世界杯32强</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959164&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Norway vs Senegal Stats: World Cup 2026 – Live</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>theanalyst</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/norway-vs-senegal-stats-world-cup-2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Norway face Senegal in Group I of the World Cup, with the Lions of Teranga hoping to quiet Erling Haaland.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>France vs Iraq Stats: World Cup 2026 – Live</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>theanalyst</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/france-vs-iraq-stats-world-cup-2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>France take on Iraq in Group I as Kylian Mbappé looks to build on his two goals against Senegal, while Iraq hope to keep their World Cup dream alive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>执教法国队取世界杯16胜，德尚与德国传奇教练舍恩并列最多</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959225&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>历史首次，法国队连续四届世界杯小组出线</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959268&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>德尚带法国队4次取得世界杯开局两连胜，但之前第3轮都没赢</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959258&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Julian Ryerson Injury: Subs off early against Senegal</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.rotowire.com/soccer/headlines/julian-ryerson-injury-subs-off-early-against-senegal-520560</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Written by RotoWire Staff
+Ryerson was forced to abandon Monday's clash against Senegal after suffering an injury in the opening minutes of the game.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>16场15球！姆巴佩追平大罗升至世界杯历史射手榜第3，距梅西3球</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-06-23 05:16:00</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-23/6a399e5a0abb8native.htm</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>德尚：登贝莱需更加释放自我，相信他将在世界杯中发挥出色</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-06-22 15:22:00</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a38e0e6eadbcnative.htm</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>巴黎人报专栏：巴尔科拉or杜埃？德尚幸福的烦恼</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:53</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5957002.html</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>巴黎人报专栏：27岁的百场先生姆巴佩，永不停步</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:42</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956979.html</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>伊布：哈兰德球商很高，不像有些球员爱强行做超出能力的事情</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-06-22 11:32</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956713.html</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>索尔巴肯：会在进攻端继续给哈兰德支持，厄德高训练状态不错</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:12</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956529.html</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>姆巴佩新闻发布会：我和奥利塞有默契；世界杯冠军最重要</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-06-22 09:30</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956504.html</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>武磊：感觉日本队每一个位置都没有短板，整体非常强大</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-06-22 08:32</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956412</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026美加墨世界杯小组赛第2轮角逐，日本队4-0大胜突尼斯队。上海海港球员武磊在连线节目中表示：“感觉日本队每一个位置都没有短板，整体非常强大。”
+武磊说道：“我觉得现在日本队整体非常强大，每一个位置感觉都比较平均，好像没有哪一个位置稍弱一点。就像刚才说的，前锋位置上，不只是一个得分点，有很多得分</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>朗尼克：如果亚马尔保持健康脚踏实地，他可能达到梅西的水平</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-06-22 07:41</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956344</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>奥地利队主帅朗尼克在他们对阵阿根廷的赛前新闻发布会上表示，如果亚马尔能保持健康并脚踏实地，有可能达到梅西的水平。
+在被问到世界杯淘汰赛是否可能碰上西班牙时，朗尼克表示路易斯-德拉富恩特执教的球队“不是任何人都想面对的对手”。
+“西班牙也是近年来书写足球历史的国家之一，而且他们还有拉明-亚马尔，这名未</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>塞内加尔主帅：哈兰德非常出色，但我们也有非常优秀的后卫</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-06-22 07:13</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956281</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>塞内加尔将在世界杯小组赛第二场对阵挪威，主帅蒂奥赛前接受了拜因体育的采访。
+不会。在我的执教理念中，我们从来不会只针对某一名球员制定比赛计划。我们知道哈兰德是一名非常出色的前锋，也是世界上最优秀的前锋之一。他只要获得半次机会，就有能力把球送进球门。与此同时，我们也拥有非常优秀的后卫，他们习惯于面对</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>塞内加尔门将：哈兰德效率非常高，但足球是一项团队运动</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-06-22 06:13</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956235.html</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>塞内加尔主帅：不会专门制定针对哈兰德的战术；后勤问题未影响球队</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-06-22 06:07</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956182</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>6月21日，在即将对阵挪威队赛前，塞内加尔主帅蒂奥接受了采访。
+是的，距离比赛已经只剩大约24小时，我们将迎来与挪威队的对决。这是一场非常困难的比赛，我们对此非常清楚。我们已经做了充分准备，对对手进行了非常细致的分析，包括他们的比赛录像、战术特点以及他们的优势和强项。
+现在球队的状态是非常专注和</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>姆巴佩：世界杯射手王？应该问梅西，我一直知道他会继续进球</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-06-22 05:20</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956141.html</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>姆巴佩：锋线三个位置我都能踢；数据无法体现登贝莱的作用</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-06-22 05:05</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956081.html</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>伊拉克主帅打趣：怎么防姆巴佩？我打算问问能不能上三个门将</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-06-22 03:58</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956032.html</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>队报：姆巴佩将出席法国对阵伊拉克的赛前发布会</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-06-22 01:34</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5955831.html</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>RMC：姆巴佩的终极挑战是走进法国人的心里</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-06-21 22:47</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5955495.html</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>尼亚凯特：哈兰德是我交手次数最多的球员之一，见他像老熟人</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-06-21 22:03</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5955400.html</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>世界杯首轮速度榜：澳大利亚后卫力压哈兰德居首，姆巴佩第9</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-06-21 09:10</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5954018.html</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>邮报盘点哈兰德奢侈品收藏：33万镑爱马仕包、28万豪华腕表</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-06-21 09:01</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5954007.html</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>队报：德尚或让迪涅、科内以及巴尔科拉首发出战伊拉克</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-06-21 06:40</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5953739.html</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>前队友：我曾担任过姆巴佩的队长，他偶像C罗且追求卓越</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/feed.html?articleId=5957296&amp;_font=m&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>队报：登贝莱清楚近期的批评，他向队友保证会在球场上回应</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5957172&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>法国3-0伊拉克，姆巴佩双响，奥利塞双助攻登贝莱传射</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959138&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>半场：挪威1-0塞内加尔，彼得森建功，哈兰德中框，厄德高失良机</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959136&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>世界杯先生，姆巴佩连续三场世界杯进球2+为历史第四人</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959147&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>姆巴佩在世界杯6次单场至少打进2球，创造世界杯新纪录</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959130&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>终于来了！三届世界杯出场13次，登贝莱攻入世界杯处子球</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959103&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>16场16球！姆巴佩追平克洛泽，升至世界杯历史射手榜第二</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959094&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>好兄弟！登贝莱在世界杯3次助攻，都传给了姆巴佩</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959082&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>姆巴佩：球队仍有提升空间，但我们正走在正确道路上</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959230&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>姆巴佩在三届世界杯攻入至少4球，为历史第三人</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959234&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Opta：哈兰德国家队近12场正式赛均进球，近21次出场18次破门</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959229&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>太简单的球我不进？哈兰德下半场梅开二度，世界杯2场打入4球</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959210&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>德尚：对登贝莱有信心，他只是没完全找到在俱乐部的那种节奏</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959186&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>强到离谱，姆巴佩百场里程碑双响，国家队100场60球40助攻</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959208&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2进球+2过人+1抢断，姆巴佩当选法国vs伊拉克全场最佳</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959194&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>挪威3-2塞内加尔提前出线，哈兰德梅开二度+中柱，萨尔双响</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959264&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>前两场世界杯都至少打进两球，哈兰德成为历史第六人</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959291&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>队报评分：奥利塞7分、登贝莱7分、姆巴佩8分</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/feed.html?articleId=5959285&amp;_font=m&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>姆巴佩双响追平克洛泽，法国兵不血刃挺进32强</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/feed.html?articleId=5959262&amp;_font=m&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>绝对大腿，哈兰德在挪威队最近12场正式比赛中打入25球</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959238&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>England offer rare peek behind the curtain with no place to hide under Tuchel</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 00</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/21/england-world-cup-training-intensity-peek-behind-curtain-thomas-tuchel</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">There was more insight at the World Cup training base than usual with intensity on the rise under Thomas Tuchel  T he tall hooded figure kept barking </t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Thomas Tuchel urges England to improve defence against Ghana after ‘wake-up call’</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 23</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/23/thomas-tuchel-england-ghana-world-cup-defence-improve</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Win over Ghana could secure top spot in the group  ‘We dropped too deep,’ Tuchel says of Croatia opener  Thomas Tuchel believes England were given a w</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>New Zealand World Cup 2026: Fixtures, manager, squad depth and tactical analysis</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>7 hours ago</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/new-zealand-world-cup-2026-fixtures-squad-analysis/</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>This summer marks New Zealand’s third appearance at a World Cup . They went unbeaten in their most recent appearance in 2010, but three draws wasn’t e</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Fans delayed entry as bad weather affects France-Iraq tie</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:21:18</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cn4d7g5xxw8o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>France against Iraq is the third game to be held at the Philadelphia Stadium at the 2026 World Cup  Bad weather delayed fans being able to enter the P</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Mbappe and Olise hint at a partnership for the ages</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-06-20T18:00:00</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/kylian-mbappe-michael-olise-france-analysis</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kylian Mbappe and Michael Olise combined to thrilling effect as France opened their campaign with a 3-1 triumph over Senegal, offering a glimpse of a </t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senegal at the World Cup 2026: Team Guide — History, Style, Players &amp; Group I</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/senegal-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>A team profile of Senegal (Lions of Teranga) at the FIFA World Cup 2026: 14th in the FIFA ranking, 4th appearance, best result the quarter-finals in 2</t>
         </is>
       </c>
     </row>
@@ -466,7 +2861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -500,6 +2895,1144 @@
           <t>摘要</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>两场比赛同开！法国vs伊拉克比赛恢复 挪威vs塞内加尔8点开球</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-06-23 08:06:37</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-23/6a39c984b4a8anative.htm</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>France vs Iraq resumes after two-hour weather delay at the World Cup</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Tue, 23 Jun 2026 00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/person/player/france-vs-iraq-resumes-after-two-hour-weather-delay-at-the-world-cup</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The World Cup 2026 match between France and Iraq in Group I has resumed after a weather break of around two hours and 15 minutes.  France vs Iraq was </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Norway v Senegal: World Cup 2026 – live</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tue Jun 23 2026 00:</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/live/2026/jun/22/norway-v-senegal-world-cup-2026-live</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>⚽️ World Cup kick-off: 8pm ET/1am BST/10am AEST ⚽️ Player guide | Bracketology | Golden Boot | Email Jeff  1 min They’re off and trotting in East Ruth</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>France v Iraq: match resumes after two-hour storm delay at World Cup 2026 – live</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tue Jun 23 2026 00:</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/live/2026/jun/22/france-v-iraq-world-cup-2026-live-updates</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚽️ World Cup kick-off: 5pm ET/10pm BST/7am AEST ⚽️ Player guide | Bracketology | Golden Boot | Email Tim  46 min The game resumes! And it’s still 1-0 </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>'There is something up with that football' Joe Hart reveals World Cup Trionda theory behind strange Kylian Mbappe and Lionel Messi phenomenon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 22</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/there-is-something-up-with-that-football-joe-hart-reveals-world-cup-trionda-theory-behind-strange-kylian-mbappe-and-lionel-messi-phenomenon</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>It wouldn't a World Cup unless there were goalkeepers complaining about the flight of the ball.  Kylian Mbappe's opener for France against Iraq on Mon</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Why is the second half of France vs Iraq delayed?</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 22</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/why-is-the-second-half-of-france-vs-iraq-delayed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>France vs Iraq's first half concluded at approximately 10:45pm British time, with the former up 1-0 through a Kylian Mbappe strike.  Mbappe , now just</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>France vs Iraq plunged into weather chaos - what are the World Cup 2026 weather protocols?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 22</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/france-vs-iraq-sees-weather-chaos-ensue-what-are-the-protocols</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>France vs Iraq is currently paused, with the former up 1-0 through a Kylian Mbappe and Michael Olise link-up in the 14th minute.  Mbappe , now just th</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>How to watch Norway vs Senegal for FREE: Live stream details for a crucial World Cup 2026 Group I</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 22</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/watch-norway-vs-senegal-free-world-cup-2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>It's always dangerous to assume anything about what lies ahead in a major tournament but Norway vs Senegal feels like Group I's decisive fixture at th</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Who is the referee for Norway vs Senegal?</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 22</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/who-is-the-referee-for-norway-vs-senegal</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Norway are set to face Senegal as World Cup's Group I reaches its second round of fixtures.  Norway are looking to build on their impressive 4-1 win o</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Norway vs Senegal prediction: Can Norway continue their fast World Cup start?</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 21</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/norway-vs-senegal-prediction-can-norway-continue-their-fast-world-cup-start</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Norway and Senegal go head-to-head tonight in what could be a thrilling match in Group I.  Erling Haaland impressed as the Norwegians got off to a str</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Who is the referee for France vs Iraq?</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 20</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/who-is-the-referee-for-france-vs-iraq</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>France lived up to their pre-tournament billing when they dispatched Senegal 3-1 in their opening Group I clash last week.  The spotlight had firmly b</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Mbappe World Cup goals: How many does the Frenchman need to overtake Lionel Messi?</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 19</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/person/player/mbappe-world-cup-goals-how-many-does-the-frenchman-need-to-overtake-lionel-messi</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Kylian Mbappe is on track to becoming the World Cup's greatest ever player, having made it to two successful finals with France at the tournament.  Th</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>How to watch France vs Iraq for FREE: Live stream details as Kylian Mbappe chases history at World Cup 2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 19</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/watch-france-vs-iraq-for-free-world-cup-2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Kylian Mbappe broke France's goalscoring record, on matchday one at the World Cup 2026 , and Les Bleus' skipper will be hungry for more as he leads hi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>France vs Iraq prediction: Will Kylian Mbappe add to his World Cup goal tally?</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 18</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/france-vs-iraq-prediction-will-kylian-mbappe-add-to-his-world-cup-goal-tally</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>You've got to feel for Iraq in Group I.  Graham Arnold's side are playing in their first World Cup for 40 years, but had to play second fiddle to Norw</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Squawka’s World Cup AI Predictor: AI score predictions for Monday June 22 at the 2026 World Cup</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>9 hours ago</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/squawkas-world-cup-ai-predictor-22-06/</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Using data from previous tournaments and qualifying, we’ve tasked our model with creating some World Cup AI predictions with correct score picks on ev</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>本届世界杯首次！RMC：法国vs伊拉克下半场补水暂停取消</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-06-23 08:06:37</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-23/6a39c8440f8e6native.htm</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>世界杯-挪威vs塞内加尔首发：哈兰德PK马内！厄德高、杰克逊出战</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-06-23 06:35:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-23/6a396818a047dnative.htm</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>World Cup Daily: France-Iraq restarts after temporary suspension due to weather</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-06-22T23:51:26</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/soccer/story/_/id/49141065/world-cup-daily-crying-belgium-fan-saved-var-messi-mbappe-haaland-action</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>It's another week of 2026 FIFA World Cup action, and we have some big teams playing today, including Argentina, France and Norway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>How do you stop Messi, Mbappe, Haaland and Kane?</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-06-22T08:10:21</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cly8gpp39d0o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Four of the most in-form strikers in world football will look to add to their red-hot starts to the World Cup this week  A World Cup is always that li</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>队报预测法国vs伊拉克首发：姆总、奥利塞、登贝莱和巴尔科拉出战</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-06-22 17:50:15</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a3900c8421e4native.htm</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>官方：挪威vs伊拉克创97%收视率 是21世纪挪威世界杯赛事第2高</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-06-22 16:43:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a38f548707e8native.htm</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>塞内加尔主帅：能执教自己的祖国参加世界杯是一种莫大的荣耀</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-06-22 01:51</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5955868.html</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Slick Spain shine as Sharks shock the Celeste</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-06-21T22:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/matchday-11-round-up-review-highlights</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Lamine Yamal got Spain scoring at the FIFA World Cup 2026™ but it was Cabo Verde who once again stole the show with a 2-2 draw against Uruguay.
+Spain</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>The World Cup records that look set to be broken</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-06-21T13:55:05</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cpv3kkv4z4mo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Lionel Messi has appeared at six World Cups, scoring 16 goals  The 2026 World Cup may only be 10 days old but the tournament has already rewritten foo</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>France vs Iraq Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-06-21T09:26:39</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/france-vs-iraq-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Can Kylian Mbappé make history as he joins France’s centurions club? Look ahead to this Group I clash at the 2026 FIFA World Cup with our France vs Ir</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Norway vs Senegal Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-06-21T09:21:55</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/norway-vs-senegal-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>After getting off to contrasting starts in their respective FIFA World Cup openers, Norway and Senegal will meet in New York in what is sure to be a h</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Argentina and France among quartet eyeing knockout stage</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-06-21T09:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/preview-matchday-twelve</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Find out all the key details as Groups I and J return to action at FIFA World Cup 2026, headlined by former winners Argentina and France.
+Argentina m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>伊拉克VS挪威这是哈兰德的第一次世界杯，如果梅开...</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-06-21 16:59</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5940517.html</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Mbappe and Olise hint at a partnership for the ages</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-06-20T18:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/kylian-mbappe-michael-olise-france-analysis</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kylian Mbappe and Michael Olise combined to thrilling effect as France opened their campaign with a 3-1 triumph over Senegal, offering a glimpse of a </t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>据报道，塞内加尔世界杯训练营一片混乱……</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-06-20 22:24</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5952852.html</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>官方：揭幕战主裁桑帕约将执法世界杯挪威vs塞内加尔</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-06-19 20:51</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5949666.html</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>France vs Iraq; FIFA World Cup Group I</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>skysports</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>10:00pm, Monday 22n</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.skysports.com/football/france-vs-iraq/report/549806</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>France                           vs Iraq. FIFA World Cup Group I.  10:00pm, Monday 22nd June 2026.  Philadelphia Stadium Attendance: Attendance 68,324</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>France vs Iraq: predictions, best bets, odds and stats</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1 hour ago</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/france-vs-iraq-predictions-tips-22-06-26/</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No previous meetings between these teams.
+No price boosts for this event.
+Bet Builder is not available yet.
+Betting markets are not available yet.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Norway vs Senegal: predictions, best bets, odds and stats</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1 hour ago</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/norway-vs-senegal-predictions-tips-23-06-26/</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No previous meetings between these teams.
+No price boosts for this event.
+Bet Builder is not available yet.
+Betting markets are not available yet.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Iraq at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/iraq-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>A team profile of Iraq (Lions of Mesopotamia), back at the FIFA World Cup after 40 years: 58th in the FIFA ranking, 2nd appearance, Graham Arnold's ta</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senegal at the World Cup 2026: Team Guide — History, Style, Players &amp; Group I</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/senegal-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>A team profile of Senegal (Lions of Teranga) at the FIFA World Cup 2026: 14th in the FIFA ranking, 4th appearance, best result the quarter-finals in 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Norway vs Senegal Stats: World Cup 2026 – Live</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>theanalyst</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/norway-vs-senegal-stats-world-cup-2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Norway face Senegal in Group I of the World Cup, with the Lions of Teranga hoping to quiet Erling Haaland.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>France vs Iraq Stats: World Cup 2026 – Live</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>theanalyst</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/france-vs-iraq-stats-world-cup-2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>France take on Iraq in Group I as Kylian Mbappé looks to build on his two goals against Senegal, while Iraq hope to keep their World Cup dream alive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Is VAR being used differently at the World Cup vs the Premier League?</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-06-22T14:39:42</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cy06881596wo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Four goals have been disallowed on VAR review at the 2026 World Cup  Complaining about the video assistant referee (VAR) has become a sport all of its</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>England offer rare peek behind the curtain with no place to hide under Tuchel</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/21/england-world-cup-training-intensity-peek-behind-curtain-thomas-tuchel</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">There was more insight at the World Cup training base than usual with intensity on the rise under Thomas Tuchel  T he tall hooded figure kept barking </t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Thomas Tuchel urges England to improve defence against Ghana after ‘wake-up call’</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 23</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/23/thomas-tuchel-england-ghana-world-cup-defence-improve</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Win over Ghana could secure top spot in the group  ‘We dropped too deep,’ Tuchel says of Croatia opener  Thomas Tuchel believes England were given a w</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>New Zealand World Cup 2026: Fixtures, manager, squad depth and tactical analysis</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>7 hours ago</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/new-zealand-world-cup-2026-fixtures-squad-analysis/</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>This summer marks New Zealand’s third appearance at a World Cup . They went unbeaten in their most recent appearance in 2010, but three draws wasn’t e</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Fans delayed entry as bad weather affects France-Iraq tie</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:21:18</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cn4d7g5xxw8o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>France against Iraq is the third game to be held at the Philadelphia Stadium at the 2026 World Cup  Bad weather delayed fans being able to enter the P</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>I组积分榜：法国力压挪威居首，末轮双方上演头名之争</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959295&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -512,7 +4045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -544,6 +4077,2784 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>摘要</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>基本确定J组第1！阿根廷淘汰赛大概率踢H组第2，碰佛得角/沙特？</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-06-23 04:24:00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-23/6a39953d6ee7anative.htm</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>佛得角主帅：乌拉圭第一个进球不干净，对阵沙特全力争胜</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:53</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956646.html</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>解说员贺宇：乌拉圭球员技术和对抗技巧上不如沙特和佛得角</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-06-22 09:08</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956469</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>在世界杯小组赛第二轮乌拉圭2-2战平佛得角赛后（前两轮，乌拉圭1-1沙特、2-2佛得角），解说员贺宇在社交媒体上谈到了乌拉圭的前两场比赛。
+解说员贺宇写道：“乌拉圭大批旅欧球员，技术和对抗技巧上这两场真的不如沙特和佛得角。这绝对不是夸张的说法。心态稳不住，首先源于各个点的质量上的滑落。这类似奥地利</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>奇迹近在眼前！佛得角末轮赢沙特铁定出线 打平也有99%概率晋级！</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-22 08:20:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a387de3e12c3native.htm</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Jordan vs Algeria prediction: Will World Cup debutants claim their first win?</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Tue, 23 Jun 2026 00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/jordan-vs-algeria-prediction-will-world-cup-debutants-claim-their-first-win</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Having seen fellow debutants Cape Verde and Curacao grab the headlines over the weekend, now is the time for Jordan to announce themselves at World Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Who are the BBC commentators and pundits for Uruguay vs Cape Verde?</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 21</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/who-are-the-bbc-commentators-and-pundits-for-uruguay-vs-cape-verde</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Cape Verde are looking to capitalise on their incredible draw against Spain with their second World Cup 2026 game, where they take on Uruguay.  Marcel</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Uruguay vs Cape Verde prediction: Can World Cup debutants pull off another shock?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 20</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/uruguay-vs-cape-verde-prediction-can-world-cup-debutants-pull-off-another-shock</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>We could be set for another compelling encounter in Group H.  You will need no reminding that Cape Verde surprised and delighted the world by claiming</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>How to watch Uruguay vs Cape Verde for FREE: Live stream details for World Cup 2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/watch-uruguay-vs-cape-verde-free-world-cup-2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Few would have predicted before the World Cup 2026 that Group H would be this tight after the opening round of fixtures, but with all four teams on on</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Alexia Putellas '100% confident' Spain can win World Cup despite Cape Verde setback</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 19</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/alexia-putellas-100-percent-confident-spain-can-win-world-cup-despite-cape-verde-setback</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alexia Putellas insists Spain’s men’s team remain firmly in contention to lift the World Cup trophy this summer despite their frustrating opening tie </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Is Lamine Yamal the youngest player to have ever scored at the World Cup?</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 16</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/person/is-lamine-yamal-the-youngest-player-to-have-ever-scored-at-the-world-cup</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Lamine Yamal bagged his first-ever World Cup goal against Saudi Arabia, making him one of the youngest scorers in the competition’s history.  Spain we</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Who is the referee for Spain vs Saudi Arabia?</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 14</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/who-is-the-referee-for-spain-vs-saudi-arabia</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>The World Cup rolls on into its 11th day with European champions Spain set to take on Saudi Arabia.  Group H remains all square with all four sides on</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>How to watch Spain vs Saudi Arabia for FREE: Live stream details as European champions aim to kickstart their World Cup 2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 14</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/watch-spain-vs-saudi-arabia-free-world-cup-2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spain take on Saudi Arabia in a World Cup 2026 Group H game from Atlanta that has more riding on it than many predicted when the draw was first made. </t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Guns for hire and gegenpress eggheads bring World Cup subplots aplenty</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/21/football-daily-geopolitics-world-cup-maverick-managerial-matchups</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>The awesome thing about a World Cup is that – unlike the Premier League where almost every elite-grade head coach comes from the same scenic Spanish t</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Spain v Saudi Arabia: World Cup 2026 – live</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sun Jun 21 2026 15:</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/live/2026/jun/21/spain-v-saudi-arabia-world-cup-2026-live</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>⚽️ Kick-off: 12pm local time/5pm BST/2am (Mon) AEST ⚽️ Player guide | Bracketology | Golden Boot | Email John  Alex Reid has penned today’s weekend sp</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cape Verde at the World Cup: African nation have gained the hearts of the world as everyone's second team after brave draw with Uruguay</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>skysports</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 07</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.skysports.com/football/news/12040/13556552/cape-verde-at-the-world-cup-african-nation-have-gained-the-hearts-of-the-world-as-everyones-second-team-after-brave-draw-with-uruguay</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Cape Verde claimed another point at the World Cup to stay unbeaten on their tournament debut; the African nation of 500,000 people showed bravery agai</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Cape Verde do it again and Lamine Yamal spurs on Spain | World Cup Daily</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 06</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/video/2026/jun/22/cape-verde-do-it-again-and-lamine-yamal-spurs-on-spain-world-cup-daily</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cape Verde do it again and Lamine Yamal spurs on Spain | World Cup Daily Max Rushden is joined by Barry Glendenning , Jeff Rueter and Mark Langdon as </t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Who will Cape Verde face in the next round?</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/team/who-will-cape-verde-face-in-the-next-round</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cape Verde are in dreamland so far in World Cup 2026.  They kicked things off with a draw against former champions Spain , and managed to score their </t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Cape Verde produce another World Cup shock as Varela strike seals Uruguay draw</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/22/cape-verde-uruguay-world-cup-group-h-match-report</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Wow. The continuation of Cape Verde’s fairytale may have serious repercussions for Marcelo Bielsa and Uruguay. The heroics of Cape Verde in holding Sp</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>World Cup 2026: Cape Verde continue remarkable story; Messi, Mbappé and Haaland return – live</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Mon Jun 22 2026 08:</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/live/2026/jun/22/world-cup-2026-cape-verde-continue-remarkable-story-messi-mbappe-and-haaland-return-live</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>⚽ All the latest news from day 11 of the tournament ⚽ Player guide | Bracketology | Golden Boot | Mail us  So what of Uruguay? I’m afraid even the wiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Uruguay v Cape Verde: World Cup 2026 – live</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Mon Jun 22 2026 00:</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/live/2026/jun/21/uruguay-v-cape-verde-world-cup-2026-live</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>⚽️ Kick-off: 6pm local time/11pm BST/8am (Mon) AEST ⚽️ Player guide | Bracketology | Golden Boot | Email Beau  90 min +7 Duarte draws a foul – honestl</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>New Zealand v Egypt: World Cup 2026 – live</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Mon Jun 22 2026 00:</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/live/2026/jun/22/fifa-world-cup-2026-live-new-zealand-v-egypt-updates-nzl-vs-egy-group-g-match-score-latest</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚽️ Kick-off time: 6pm local/11am AEST/2am BST/9pm EDT ⚽️ Player guide | Bracketology | Golden Boot | Mail Jonathan  The Pharaohs are also unchanged!  </t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Spain vs Saudi Arabia; FIFA World Cup Group H</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>skysports</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>5:00pm, Sunday 21st</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.skysports.com/football/spain-vs-saudi-arabia/report/549804</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Spain                           vs Saudi Arabia. FIFA World Cup Group H.  5:00pm, Sunday 21st June 2026.  Mercedes-Benz Stadium Attendance: Attendance</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Duarte brothers celebrate Cape Verde's latest World Cup upset: 'We could have even won here'</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-06-22T08:56:10</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/espn/story/_/id/49142000/even-won-here</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Cape Verde won hearts again in a 2-2 draw World Cup with Uruguay. Laros Duarte and Deroy Duarte were proud of the performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FIFA World Cup 2026 stats: Yamal youngest since Pele, Egypt's long-awaited first, Cape Verde's first goals</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-06-22T03:57:13</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/soccer/story/_/id/49140389/fifa-world-cup-2026-stats-lamine-yamal-youngest-pele-egypt-mohamed-salah-long-awaited-first-cape-verde-first-goals</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ESPN's By The Numbers brings you best stats from the World Cup action on June 21.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Maximiliano Araújo gets a 7.9 Sofascore Rating in his second game in the World Cup. One goal and assist against Cape Verde</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-06-22T03:09:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/maximiliano-araujo-gets-a-7-9-sofascore-rating-in-his-second-game-in-the-world-cup-one-goal-and-assist-against-cape-verde</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Cape Verde cause another World Cup shock to deny Uruguay</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-06-22T01:55:47</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/soccer/story/_/id/49139293/cape-verde-uruguay-2026-world-cup-upset</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Cape Verde's magical start to its first World Cup isn't over. It might just be getting started.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>One of World Cup's great stories - can Cape Verde become legends?</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-06-22T01:53:23</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/c0qylwk421eo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Cape Verde continue to surprise with entertaining Uruguay draw  Cape Verde's World Cup campaign will go down in history - and they are now on the cusp</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>How Cape Verde impressed again in draw with Uruguay</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-06-22T01:02:32</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/video/clip/_/id/49139731/how-cape-verde-impressed-again-draw-uruguay</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>How Cape Verde impressed again in draw with Uruguay
+Wyndham Clark talks 'surreal' feeling of winning his second U.S. Open
+Rafael Devers visibly upse</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Cape Verde score first World Cup goals to share points with Uruguay</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-06-22T00:52:27</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/video/clip/_/id/49139607/cape-verde-score-first-world-cup-goals-share-points-uruguay</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>The first World Cup goals for Cape Verde in a 2-2 draw with Uruguay spark amazing on-field celebrations, with the African nation's chances of progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Uruguay v Cape Verde</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-06-22T00:30:13</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>http://www.espn.com/soccer/report/_/gameId/760450</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Cape Verde created fresh waves at the World Cup as they held two-time champions Uruguay to a 2-2 draw in a high-octane encounter in Miami.
+Kevin Pina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Uruguay 2-2 Cape Verde Stats: Pina Makes History as World Cup Debutants Battle to Another Draw</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-06-22T00:26:22</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/uruguay-vs-cape-verde-stats-world-cup-group-h-live/</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Cape Verde put in another brilliant display and made history on their way to a 2-2 draw against Uruguay as they sprang another sur prise at the 2026 F</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Spain find spark in Yamal's return</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-06-22T00:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/spain-reaction-lamine-yamal-luis-de-la-fuente-alex-baena</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Spain produced a vastly improved display to sweep aside Saudi Arabia, with Lamine Yamal inspiring a convincing 4-0 victory at the FIFA World Cup 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>直播吧世界杯日报：佛得角2连平再创历史 埃及取队史世界杯首胜</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-06-22 17:50:15</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a38ecf17fdf9native.htm</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>撞上大魔王？32强最新预测：佛得角碰阿根廷！埃及头名力压比利时</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-06-22 16:29:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a38f16371d91native.htm</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>世界杯午报：佛得角延续黑马本色，埃及逆转取得世界杯首胜</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-06-22 13:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956826.html</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>佛得角门将收不续约通知登顶热搜，实际球员世界杯前已告别球队</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-06-22 12:31</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956790.html</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>为佛得角攻入队史世界杯首球，皮纳当选与乌拉圭一役全场最佳</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-06-22 11:31</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956730.html</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>世界杯H组 佛得角励志两连平</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-06-22 11:15</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956710.html</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>佛得角再平世界冠军，非洲岛国书写世界杯梦幻篇章</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-06-22 09:57</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956545.html</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>达瓦萨里：尽管输球，但我们仍然是世界上最强大的球队之一</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-06-22 09:16</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956479</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>世界杯小组赛第二轮，沙特0-4不敌西班牙赛后，沙特国脚达瓦萨里接受了瞬采。
+达瓦萨里表示：“我们必须改正错误，输球是足球的一部分，我们将在最后一场对阵佛得角的比赛中努力弥补。”
+“与西班牙这样的强队交手，能增强我们在世界杯这样规模的赛事中的能力和经验，未来会更好。”
+“尽管沙特国家队惨败于西班牙队，</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>opta的H组预测：佛得角62.25%出线，乌拉圭41.2%</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-06-22 09:07</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956477</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>opta的预测显示，H组的佛得角出线概率为62.25%，乌拉圭则是41.2%。
+目前H组西班牙积4分排名第1，乌拉圭和佛得角同积2分，净胜球都是0，乌拉圭因多进1球排名第2。但由于乌拉圭最后一轮要踢西班牙，佛得角的对手则是沙特，opta更看好佛得角的出线可能。沙特虽然目前排名垫底，但和乌拉圭、佛得</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>西班牙若头名出线将遇J组第二，若小组第二可能首轮碰阿根廷</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-06-22 08:38</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956424</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>美加墨世界杯小组赛两轮过后，在H组，西班牙两战积4分，乌拉圭与佛得角积2分，沙特积1分。最后一轮比赛，西班牙将与乌拉圭直接对话。
+对于H组来说，小组第一和小组第二出线后的形势可能有着天壤之别。 H1将在1/16决赛碰J2， 也就是阿根廷、奥地利所在小组的第二名，而H2将在1/16决赛碰J1，从目前</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>世界杯名画！比尼亚斯帮佛得角球员压腿，见进攻有利放下腿就跑</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-06-22 08:23</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956406</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>在美加墨世界杯小组赛乌拉圭2-2佛得角的比赛中，发生了一个载入史册的名场面。
+比赛进行到第43分钟时，佛得角队阿尔坎若倒在地上，乌拉圭队前锋比尼亚斯帮他压腿，但主裁判并没有吹停比赛。
+这时，乌拉圭队形成进攻，比尼亚斯见到球队形成攻势，放下阿尔坎若的腿，转身就扎进了对方的禁区里。虽然他没有直接参与</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>这场摸鱼，佛得角门将沃齐尼亚对阵乌拉圭没有完成扑救</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-06-22 08:14</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956388</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>佛得角2-2战平乌拉圭的比赛中，首轮表现亮眼的沃齐尼亚这回“美美隐身”了。
+本场比赛，乌拉圭全场只有2次射正，但都取得了进球，沃齐尼亚没能完成哪怕一次扑救。上轮对阵西班牙，沃齐尼亚7次扑救力保球门不失。
+不过今天，沃齐尼亚的队友给力，皮纳和瓦雷拉分别进球，帮助佛得角2-2战平乌拉圭。
+相关标签
+佛得</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>世界杯H组积分榜：西班牙4分领跑，乌拉圭、佛得角均2分</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-06-22 08:05</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956355</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>北京时间6月22日，2026年世界杯结束了小组赛H组第2轮的全部较量。
+首轮爆冷战平的西班牙在本轮比赛中4-0大胜沙特阿拉伯，从而以4分在小组当中领跑，而且4个净胜球也遥遥领先其他同组对手。
+乌拉圭和世界杯新军佛得角在经历一场大战之后2-2战平，这使得他们都取得了两连平的战绩。乌拉圭凭借进球数的</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>黑马？！佛得角2-2平乌拉圭 皮纳斩佛得角世界杯首球穆斯莱拉送礼</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-06-22 08:04:00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/match1869180date2026vnative.htm</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>西班牙足协主席：首胜正是我们所需要的，我们有实力赢世界杯</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-06-22 07:55</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956352</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>在西班牙4-0大胜沙特阿拉伯，取得本届世界杯首胜之后，身为西班牙足协主席的拉斐尔-卢赞接受了媒体的采访。
+卢赞表示：“我很享受，因为我觉得这正是我们需要的。首轮经历了小低谷之后，现在我们在享受这场重要胜利，也已经开始考虑下一场比赛。”
+谈到球队在战平佛得角后的情绪时，卢赞表示球员们“非常非常投入</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>40岁穆斯莱拉此前离开国家队3年，回归后在世界杯连场失误</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-06-22 07:49</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956356</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>美加墨世界杯小组赛第2轮，在乌拉圭与佛得角的比赛中，40岁的乌拉圭门将穆斯莱拉出击失误，导致球队丢球。而在上轮与沙特的比赛中，他就因脱手失误导致球队丢球。
+据统计，穆斯莱拉在世界杯四次因失误导致丢球，为有统计以来最多。
+实际上，从2022年到2025年，穆斯莱拉在这四个自然年里只为乌拉圭出战两场</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>穆斯莱拉世界杯4次失误导致丢球，有统计以来所有门将最多</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-06-22 07:48</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956354</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>北京时间6月22日，在世界杯H组第二轮乌拉圭和佛得角的比赛中，现年40岁的穆斯莱拉第61分钟出现出击失误，随后被打空门得手并且将比分追平为2-2。
+根据Opta的统计，这是穆斯莱拉职业生涯至今在世界杯上第4次因失误导致本队丢球，他也就此超越了诺伊尔、施瓦泽以及代亚耶亚(均为3次)，成为自1966年有</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>奥尔莫：首战后全队心情都不好，这场我们给出了非常好的回应</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-06-22 07:31</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956321</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>西班牙在本届世界杯小组赛第二场4-0战胜沙特，奥尔莫赛后接受了sportyTV的采访。
+真的非常开心。当然，在第一场比赛之后，我们的目标就是拿下本届世界杯的首场胜利。我觉得球队这场比赛的回应非常出色，我们继续创造了很多机会，而且这一次把不少机会转化为了进球。所以我们会好好庆祝这场胜利，我也感到非常</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>生涯前两场世界杯均进球，马克西-阿劳霍成乌拉圭1954年以来首人</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-06-22 07:16</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956308</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>北京时间6月22日，在世界杯H组第二轮的比赛中，马克西-阿劳霍第44分钟打进扳平比分的关键进球，帮助乌拉圭在半场过后2-1逆转领先于佛得角。
+根据Stats Foot的统计，算上小组首轮面对沙特的进球，目前效力于葡萄牙体育的马克西-阿劳霍也就此成为自1954年的奥斯卡-明格斯以来，乌拉圭队首位在自己</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>创造历史，佛得角是首支靠任意球取得世界杯首球的球队</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-06-22 06:52</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956278</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>美加墨世界杯小组赛第2轮，佛得角在与乌拉圭的比赛中取得了队史世界杯首球，凯文-皮纳的进球为佛得角创造历史。
+据Opta数据统计，自1966年有详细数据统计以来，佛得角是首支依靠直接任意球取得队史世界杯首球的球队。
+同时，凯文-皮纳也是世界杯史上第3位取得直接任意球进球的非洲球员，前两位是2022年世</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>不虚此行！新军佛得角、库拉索、约旦、乌兹均取得世界杯首球</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-06-22 06:32</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956261</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026年美加墨世界杯扩军至48支球队，佛得角、库拉索、约旦、乌兹别克斯坦成为了本届世界杯的四支新军。在佛得角队取得历史性首球后，本届世界杯的四支新军都已经取得进球，其中佛得角和库拉索还实现了拿一分的目标。
+佛得角世界杯首秀0-0逼平西班牙，就已经足够令人震惊，他们又在与乌拉圭的比赛中由凯文-皮纳</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>佛得角队史世界杯首球！皮纳超远任意球重炮，攻破乌拉圭球门！</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-06-22 06:21:00</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a3863db0eb5bnative.htm</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>亚马尔打进世界杯首球后社媒回怼沙特球迷：我在这里</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-06-22 04:28</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956072.html</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>西班牙4-0沙特，亚马尔世界杯处子球，奥亚萨瓦尔两射一传</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-06-22 02:01</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5955874</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>北京时间6月22日世界杯小组赛第2轮，西班牙对阵沙特阿拉伯。上半场，奥亚萨瓦尔助攻，亚马尔收获个人世界杯处子球。随后，奥亚萨瓦尔在3分钟时间内完成双响。下半场，库库雷利亚射门造成坦巴蒂乌龙。全场比赛结束，西班牙4-0轻取沙特。
+第11分钟，奥亚萨瓦尔横传，亚马尔后点铲射，西班牙1-0！
+第21分</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Slick Spain shine as Sharks shock the Celeste</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-06-21T22:00:00</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/matchday-11-round-up-review-highlights</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Lamine Yamal got Spain scoring at the FIFA World Cup 2026™ but it was Cabo Verde who once again stole the show with a 2-2 draw against Uruguay.
+Spain</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Uruguay vs Cape Verde Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-06-21T21:19:13</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/uruguay-vs-cape-verde-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Can Bubista’s team produce another shock in Group H at the FIFA World Cup ? We look ahead to Sunday’s clash with our Uruguay vs Cape Verde prediction </t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Spain 4-0 Saudi Arabia: World Cup Group H report</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-06-21T20:36:30</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/spain-4-0-saudi-arabia-world-cup-group-h-report</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>De la Fuente: Spain are a family</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-06-21T20:00:00</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/luis-de-la-fuente-spain-father-figure</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Spain coach Luis de la Fuente was like a proud papa watching his side take down Saudi Arabia on his 65th birthday.
+Luis de la Fuente turned 65 during</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Lamine Yamal shows why this could be his World Cup</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-06-21T19:27:01</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cj0gy46d5vro?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'He's the main man!' - Rooney on Lamine Yamal  Lamine Yamal was the story before kick-off and is dominating conversation long after the final whistle </t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Lamine Yamal Arrives at the World Cup to Play Role as Spain’s Inspiration</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>theanalyst</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:36:14</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/lamine-yamal-arrives-world-cup-stats-2026-spain</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Lamine Yamal made his first FIFA World Cup start on Sunday, and he quickly ensured Spain weren’t going to endure the same frustrations as in their hum</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Lamine Yamal Arrives at the World Cup to Play Role as Spain’s Inspiration</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:36:14</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/lamine-yamal-arrives-world-cup-stats-2026-spain/</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Lamine Yamal made his first FIFA World Cup start on Sunday, and he quickly ensured Spain weren’t going to endure the same frustrations as in their hum</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Spain 4-0 Saudi Arabia Stats: Mikel Oyarzabal and Lamine Yamal Lead First-Half Blitz</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>theanalyst</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:23:10</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/spain-vs-saudi-arabia-stats-world-cup-group-h</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>The European champions bounced back with a devastating performance to get their first win of the 2026 World Cup . Analyse the game here with our Spain</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>World Cup on Fubo: Free trials, deals, offers, subscriptions, plans and more</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>goal_pw</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:22:43</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/en/news/world-cup-2026-fubo/blt5f97df30090df47f</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOAL explains how fans can stream live 2026 FIFA World Cup matches with Fubo
+The 2026 FIFA World Cup is officially underway, treating soccer fans to </t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Spain send statement with Saudi success</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:00:00</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/spain-saudi-arabia-highlights-match-report</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>This is a modal window.
+Oyarzabal and Yamal on target in dominant display as Luis de la Fuente's side showed their class with a comprehensive Group H</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Today's World Cup 2026 Kickoff Times: Complete Pacific Time (PT) Schedule</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>goal_pw</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-06-21T17:04:43</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/en/news/world-cup-2026-pacific-time-schedule/blt708391eb6f8f1517</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Pacific Time Zone
+The 2026 FIFA World Cup has completely tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Today's World Cup 2026 Kickoff Times: Complete Mountain Time (MT) Schedule</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>goal_pw</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-06-21T16:35:30</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/en/news/world-cup-2026-mountain-time-schedule/blt2141270bc47c494f</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Mountain Time Zone
+The 2026 FIFA World Cup has completely ta</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Today's World Cup 2026 Kickoff Times: Complete Eastern Time (ET) Schedule</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>goal_pw</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-06-21T16:11:53</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/en/news/world-cup-2026-eastern-time/blt57a4c6b10cc97d94</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Eastern Time Zone
+The 2026 FIFA World Cup has completely tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Spain vs Saudi Arabia: Group H preview, odds</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-06-21T10:00:00</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/spain-vs-saudi-arabia-group-h-preview-odds</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Spain face Saudi Arabia in Atlanta. We break down form, head‑to‑head, tactics, players to watch and decimal odds, with live tracking on Sofascore.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>The best photos from matchday 11</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-06-21T05:00:00</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/best-photos-matchday-11</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Take a look through a selection of the best photos from the FIFA World Cup 26's eleventh matchday.
+The stunning scene set prior to Spain taking on Sa</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Spain vs Saudi Arabia Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-06-21T03:50:00</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/spain-vs-saudi-arabia-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Spain will feel they have a point to prove against Saudi Arabia after a disappointing opening draw with Cape Verde at World Cup 2026. Look ahead to th</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>The calm behind Cabo Verde's World Cup surprise</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-06-20T23:30:00</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/cabo-verde-stay-calm-spain-surprise-uruguay-test</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>After earning a historic point against Spain on their World Cup debut, Bubista's Cabo Verde have quickly shifted their focus to Uruguay.
+Many predict</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>世界杯首轮扑救榜：沙特门将9次居首；亚足联5支球队门将上榜</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-06-19 20:57</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5949603.html</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Spain vs Saudi Arabia team news and predicted XIs</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>19 hours ago</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/spain-vs-saudi-arabia-team-news-predicted-xis/</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Spain take on Saudi Arabia in a bid to get their 2026 World Cup campaign up and running with a win on Sunday at 5pm (UK time).
+La Roja were left frus</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Spain vs Saudi Arabia Bet Builder Tip: La Roja backed to recover in 12/1 punt</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>19 hours ago</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/spain-vs-saudi-arabia-bet-builder-21-06-26-world-cup/</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Spain will be desperate to respond after their surprise stalemate when they face Saudi Arabia in their second Group H game at the 2026 World Cup . Con</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Uruguay vs Cape Verde team news and predicted XIs</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>18 hours ago</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/uruguay-vs-cape-verde-team-news-predicted-xis/</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Cape Verde face another major test at the 2026 World Cup as they go from a shock opening draw with Spain straight into a meeting with Uruguay on Sunda</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Saudi Arabia World Cup 2026: Fixtures, results, manager, squad depth and tactical analysis</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>15 hours ago</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/saudi-arabia-world-cup-2026-fixtures-results-squad-analysis/</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saudi Arabia ’s 2026 World Cup campaign has been a mixed one so far, beginning with a disciplined draw against Uruguay before a heavy defeat to Spain </t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Spain World Cup 2026: Fixtures, results, manager, squad depth and tactical analysis</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>15 hours ago</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/spain-world-cup-2026-fixtures-results-squad-analysis/</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Spain ’s 2026 World Cup campaign took a sharp turn in North America as they followed up a frustrating opening draw with Cape Verde by producing a comm</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Uruguay vs Cape Verde Bet Builder: Uruguay to dominate in our 13/1 tip for tonight</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>13 hours ago</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/uruguay-vs-cape-verde-bet-builder-21-06-2026/</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Uruguay will look to bring Cape Verde ‘s impressive unbeaten start to the 2026 World Cup to an end when the two nations meet in Group H at Hard Rock S</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Uruguay vs Cape Verde; FIFA World Cup Group H</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>skysports</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>11:00pm, Sunday 21s</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://www.skysports.com/football/uruguay-vs-cape-verde/report/549805</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Uruguay                           vs Cape Verde. FIFA World Cup Group H.  11:00pm, Sunday 21st June 2026.  Hard Rock Stadium Attendance: Attendance 64</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Cape Verde at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/cape-verde-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>A team profile of Cape Verde (Blue Sharks), who reached a first-ever FIFA World Cup: 68th in the FIFA ranking, a half-million-population island nation</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Saudi Arabia at the World Cup 2026: Team Guide — History, Style, Players &amp; Group H</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/saudi-arabia-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>A team profile of Saudi Arabia (Green Falcons), who beat Argentina in 2022: 61st in the FIFA ranking, 7th appearance, best result Round of 16 in 1994,</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Gilson Benchimol News: Lone striker in battle</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://www.rotowire.com/soccer/headlines/gilson-benchimol-news-lone-striker-in-battle-520464</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Written by RotoWire Staff
+Gilson Benchimol recorded no stats in Sunday's 2-2 draw versus Uruguay.
+Benchimol spearheaded Cape Verde's attack as the l</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Steven Moreira News: Three tackles in draw</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://www.rotowire.com/soccer/headlines/steven-moreira-news-three-tackles-in-draw-520463</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Written by RotoWire Staff
+Moreira had three tackles (three won), two clearances and one interception in Sunday's 2-2 draw versus Uruguay.
+Moreira go</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Garry Rodrigues News: Starts on left wing</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://www.rotowire.com/soccer/headlines/garry-rodrigues-news-starts-on-left-wing-520462</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Written by RotoWire Staff
+Rodrigues generated one cross (one accurate) and one tackle in Sunday's 2-2 draw against Uruguay.
+Rodrigues got the start </t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Pico News: Brillant outing in defense</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://www.rotowire.com/soccer/headlines/pico-news-brillant-outing-in-defense-520460</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Written by RotoWire Staff
+Pico registered one shot (zero on goal) in Sunday's 2-2 draw against Uruguay.
+Pico teamed up with Diney at center-back and</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Diney News: Part of resilient back line</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://www.rotowire.com/soccer/headlines/diney-news-part-of-resilient-back-line-520459</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Written by RotoWire Staff
+Diney generated one shot (zero on goal) in Sunday's 2-2 draw versus Uruguay. In addition, he was given a yellow card in the</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Who is Kevin Pina?</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 23</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/person/player/who-is-kevin-pina</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Cape Verdean midfielder Kevin Pina has etched his name into his country’s and the World Cup’s history books.  The small island nation – a population o</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Argentina vs Austria; FIFA World Cup Group J</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>skysports</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>6:00pm, Monday 22nd</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://www.skysports.com/football/argentina-vs-austria/report/549808</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Argentina                           vs Austria. FIFA World Cup Group J.  6:00pm, Monday 22nd June 2026.  Dallas Stadium Attendance: Attendance 70,649.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>6 days ago</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
+Get the latest World Cup Group A betting odds </t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Uruguay 2-2 Cabo Verde: Araújo’s spark lights up Group H</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-06-22T02:32:18</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/uruguay-2-2-cabo-verde-araujos-spark-lights-up-group-h</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>贝尔萨：我们在某些时刻让出了比赛主导权，双方差距随之缩小</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-06-22 09:11</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956460</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026世界杯H组第二轮小组赛，乌拉圭2-2佛得角。赛后，乌拉圭主帅贝尔萨接受了DSports采访。
+关于本场比赛，贝尔萨表示：“我们未能在场上拉开实质性的差距。而当我们在一些时间段内主动让出比赛的主导权时，两队之间的实力差距也就随之被缩小了。”
+当被问及下半场巴尔韦德被安排到左路的影响时，贝尔</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>逼平乌拉圭！佛得角FIFA排名上升4名，来到第63位</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-06-22 08:13</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956387</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>北京时间6月22日，佛得角在H组的第二轮小组赛中2-2逼平南美豪强乌拉圭，他们的FIFA排名也来到第63位。
+在本场逼平乌拉圭后，
+佛得角的
+FIFA排名上升4名，来到第63位。而乌拉圭的
+FIFA排名下降3名，来到第19位。
+相关标签
+佛得角
+乌拉圭
+全部评论（115）
+🔥 热门
+萨蒙
+179 👍</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>自1966年以来，乌拉圭首次世界杯半场过后逆转比分</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-06-22 07:32</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956335</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>北京时间6月22日，在世界杯H组第二轮的比赛中，马克西-阿劳霍和卡诺比奥上半时最后时刻连下两城，帮助乌拉圭在开场21分钟先丢球的情况下，半场过后2-1逆转领先于佛得角。
+根据Stats Foot的统计，马克西-阿劳霍和卡诺比奥上半时最后阶段的两粒进球也让乌拉圭队自1966年世界杯小组赛对阵法国(半场</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>40岁的穆斯莱拉第18次在世界杯登场，超卡瓦尼乌拉圭队史第一</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-06-22 06:21</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956243</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>北京时间6月22日，在世界杯H组第二轮乌拉圭与佛得角的比赛中，现年40岁的穆斯莱拉代表乌拉圭首发出场。
+根据Stats Foot的统计，这是穆斯莱拉职业生涯至今第18次代表乌拉圭在世界杯的比赛中登场，他也就此超越了前队友卡瓦尼(17场)，独占乌拉圭队史世界杯出场数第一。
+穆斯莱拉此前曾代表乌拉圭国家</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>'Oh my word!' - Cape Verde take shock lead against Uruguay</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-06-21T22:46:33</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/videos/cjwg6le7193o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'Oh my word!' - Cape Verde take shock lead against Uruguay This content is not available in your location. There was an error Cape Verde's Kevin Pina </t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>'He's arrived' - Lamine Yamal scores the opener for Spain</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-06-21T16:31:27</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/videos/c1jyr87472jo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>'He's arrived' - Lamine Yamal scores the opener for Spain This content is not available in your location. There was an error Spain's Lamine Yamal scor</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Argentina vs Austria Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-06-21T09:34:56</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/argentina-vs-austria-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Can Austria stop Lionel Messi making FIFA World Cup history and securing another win for Argentina? We look ahead to the game with our Argentina vs Au</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Argentina and France among quartet eyeing knockout stage</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-06-21T09:00:00</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/preview-matchday-twelve</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Find out all the key details as Groups I and J return to action at FIFA World Cup 2026, headlined by former winners Argentina and France.
+Argentina m</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Argentina vs Austria: predictions, best bets, stats &amp; odds</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>1 hour ago</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/argentina-vs-austria-predictions-betting-tips-22-06-26/</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No previous meetings between these teams.
+No price boosts for this event.
+Bet Builder is not available yet.
+Betting markets are not available yet.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Tunisia World Cup 2026: Fixtures, results, manager, squad depth and tactical analysis</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>1 day ago</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/tunisia-world-cup-2026-fixtures-results-squad-analysis/</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Tunisia have never reached the knockout stages of the World Cup and will miss out yet again. They’ve bowed out at the group stage in each of their sev</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Federico Vinas News: Kept in check by Cape Verde</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.rotowire.com/soccer/headlines/federico-vinas-news-kept-in-check-by-cape-verde-520559</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Written by RotoWire Staff
+Viñas recorded zero shots, won six duels, and suffered one foul in Sunday's 2-2 draw with Cape Verde.
+After firing off fiv</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Fernando Muslera News: Makes costly mistake in draw</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://www.rotowire.com/soccer/headlines/fernando-muslera-news-makes-costly-mistake-in-draw-520558</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Written by RotoWire Staff
+Muslera made two saves in Sunday's 2-2 draw with Cape Verde.
+Muslera had relatively little to do for periods of the match </t>
         </is>
       </c>
     </row>
@@ -558,7 +6869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -593,6 +6904,3125 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>打平就晋级，西班牙队末轮战平乌拉圭大概率将小组第一出线</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:47</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956609.html</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>乌拉圭中卫卡塞雷斯：没拿到三分令人沮丧；西班牙队实力很强</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:08</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956556.html</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>世界杯H组积分榜：西班牙4分领跑，乌拉圭、佛得角均2分</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-06-22 08:05</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956355</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>北京时间6月22日，2026年世界杯结束了小组赛H组第2轮的全部较量。
+首轮爆冷战平的西班牙在本轮比赛中4-0大胜沙特阿拉伯，从而以4分在小组当中领跑，而且4个净胜球也遥遥领先其他同组对手。
+乌拉圭和世界杯新军佛得角在经历一场大战之后2-2战平，这使得他们都取得了两连平的战绩。乌拉圭凭借进球数的</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>连平世界冠军！佛得角首战0-0西班牙获首分，今天2-2乌拉圭斩首球</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-22 08:04:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a38776c1bc91native.htm</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Spain's 2026 World Cup home kit leaked</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>90min</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Wed, 24 Sep 2025 00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.90min.com/spain-2026-world-cup-home-kit-leaked?utm_source=RSS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Reigning European champions Spain are tipped as one of the favourites for the 2026 World Cup â and now, fans have been given a first look at the kit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Who is Kevin Pina?</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 23</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/person/player/who-is-kevin-pina</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Cape Verdean midfielder Kevin Pina has etched his name into his country’s and the World Cup’s history books.  The small island nation – a population o</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Who are the BBC commentators and pundits for Uruguay vs Cape Verde?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 21</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/who-are-the-bbc-commentators-and-pundits-for-uruguay-vs-cape-verde</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Cape Verde are looking to capitalise on their incredible draw against Spain with their second World Cup 2026 game, where they take on Uruguay.  Marcel</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Uruguay vs Cape Verde prediction: Can World Cup debutants pull off another shock?</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/uruguay-vs-cape-verde-prediction-can-world-cup-debutants-pull-off-another-shock</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>We could be set for another compelling encounter in Group H.  You will need no reminding that Cape Verde surprised and delighted the world by claiming</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Who is the referee for Uruguay vs Cape Verde?</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 20</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/who-is-the-referee-for-uruguay-vs-cape-verde</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uruguay have a great chance to register their first World Cup 2026 win at the Hard Rock Stadium in Miami, where they face Cape Verde.  The latter may </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>How to watch Uruguay vs Cape Verde for FREE: Live stream details for World Cup 2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 20</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/watch-uruguay-vs-cape-verde-free-world-cup-2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Few would have predicted before the World Cup 2026 that Group H would be this tight after the opening round of fixtures, but with all four teams on on</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Alexia Putellas '100% confident' Spain can win World Cup despite Cape Verde setback</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 19</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/alexia-putellas-100-percent-confident-spain-can-win-world-cup-despite-cape-verde-setback</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alexia Putellas insists Spain’s men’s team remain firmly in contention to lift the World Cup trophy this summer despite their frustrating opening tie </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Who is the referee for Spain vs Saudi Arabia?</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 14</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/who-is-the-referee-for-spain-vs-saudi-arabia</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>The World Cup rolls on into its 11th day with European champions Spain set to take on Saudi Arabia.  Group H remains all square with all four sides on</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>How to watch Spain vs Saudi Arabia for FREE: Live stream details as European champions aim to kickstart their World Cup 2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 14</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/watch-spain-vs-saudi-arabia-free-world-cup-2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spain take on Saudi Arabia in a World Cup 2026 Group H game from Atlanta that has more riding on it than many predicted when the draw was first made. </t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Guns for hire and gegenpress eggheads bring World Cup subplots aplenty</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 13</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/21/football-daily-geopolitics-world-cup-maverick-managerial-matchups</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>The awesome thing about a World Cup is that – unlike the Premier League where almost every elite-grade head coach comes from the same scenic Spanish t</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Quiz! Can you name every Spain player from their 2008, 2010 and 2012 tournament-winning squads?</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 07</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/quiz/football-quiz-can-you-name-every-spain-player-from-their-2008-2010-and-2012-tournament-winning-squads</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLAY NOW You can play all FourFourTwo quizzes right HERE  The last country to win the World Cup for the first time, Spain are a full-blown superpower </t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Spain v Saudi Arabia: World Cup 2026 – live</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sun Jun 21 2026 15:</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/live/2026/jun/21/spain-v-saudi-arabia-world-cup-2026-live</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>⚽️ Kick-off: 12pm local time/5pm BST/2am (Mon) AEST ⚽️ Player guide | Bracketology | Golden Boot | Email John  Alex Reid has penned today’s weekend sp</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Semenyo and Ghana out to emulate 2010 World Cup heroes as they face England</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 18</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/22/antoine-semenyo-ghana-2010-world-cup-team-england</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Carlos Queiroz’s squad hope to repeat the form that almost made Ghana the first African team to reach the semi-finals  A ntoine Semenyo was only 10 ye</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Who are ya? Behind the scenes of the official World Cup portrait photographs</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 09</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/22/behind-the-scenes-official-world-cup-portrait-photographs</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Poses and backstage snaps showcase the players’ personalities and the mechanics of Fifa’s obligatory photoshoots  L ionel Messi of Argentina stands ri</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Cape Verde at the World Cup: African nation have gained the hearts of the world as everyone's second team after brave draw with Uruguay</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>skysports</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 07</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.skysports.com/football/news/12040/13556552/cape-verde-at-the-world-cup-african-nation-have-gained-the-hearts-of-the-world-as-everyones-second-team-after-brave-draw-with-uruguay</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Cape Verde claimed another point at the World Cup to stay unbeaten on their tournament debut; the African nation of 500,000 people showed bravery agai</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Cape Verde do it again and Lamine Yamal spurs on Spain | World Cup Daily</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 06</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/video/2026/jun/22/cape-verde-do-it-again-and-lamine-yamal-spurs-on-spain-world-cup-daily</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cape Verde do it again and Lamine Yamal spurs on Spain | World Cup Daily Max Rushden is joined by Barry Glendenning , Jeff Rueter and Mark Langdon as </t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Spain have Lamine Yamal back and finally resemble World Cup contenders</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>espn</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 03</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/soccer/story/_/id/49136564/spain-lamine-yamal-back-resemble-world-cup-contenders</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Who will Cape Verde face in the next round?</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/team/who-will-cape-verde-face-in-the-next-round</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cape Verde are in dreamland so far in World Cup 2026.  They kicked things off with a draw against former champions Spain , and managed to score their </t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Cape Verde produce another World Cup shock as Varela strike seals Uruguay draw</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/22/cape-verde-uruguay-world-cup-group-h-match-report</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Wow. The continuation of Cape Verde’s fairytale may have serious repercussions for Marcelo Bielsa and Uruguay. The heroics of Cape Verde in holding Sp</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>World Cup 2026: Cape Verde continue remarkable story; Messi, Mbappé and Haaland return – live</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Mon Jun 22 2026 08:</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/live/2026/jun/22/world-cup-2026-cape-verde-continue-remarkable-story-messi-mbappe-and-haaland-return-live</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>⚽ All the latest news from day 11 of the tournament ⚽ Player guide | Bracketology | Golden Boot | Mail us  So what of Uruguay? I’m afraid even the wiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Uruguay v Cape Verde: World Cup 2026 – live</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Mon Jun 22 2026 00:</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/live/2026/jun/21/uruguay-v-cape-verde-world-cup-2026-live</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>⚽️ Kick-off: 6pm local time/11pm BST/8am (Mon) AEST ⚽️ Player guide | Bracketology | Golden Boot | Email Beau  90 min +7 Duarte draws a foul – honestl</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>New Zealand v Egypt: World Cup 2026 – live</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Mon Jun 22 2026 00:</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/live/2026/jun/22/fifa-world-cup-2026-live-new-zealand-v-egypt-updates-nzl-vs-egy-group-g-match-score-latest</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚽️ Kick-off time: 6pm local/11am AEST/2am BST/9pm EDT ⚽️ Player guide | Bracketology | Golden Boot | Mail Jonathan  The Pharaohs are also unchanged!  </t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Argentina vs Austria; FIFA World Cup Group J</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>skysports</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>6:00pm, Monday 22nd</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.skysports.com/football/argentina-vs-austria/report/549808</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Argentina                           vs Austria. FIFA World Cup Group J.  6:00pm, Monday 22nd June 2026.  Dallas Stadium Attendance: Attendance 70,649.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Spain vs Saudi Arabia; FIFA World Cup Group H</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>skysports</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>5:00pm, Sunday 21st</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.skysports.com/football/spain-vs-saudi-arabia/report/549804</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Spain                           vs Saudi Arabia. FIFA World Cup Group H.  5:00pm, Sunday 21st June 2026.  Mercedes-Benz Stadium Attendance: Attendance</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Spain at the men's World Cup: All-time results and stats</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-06-22T04:50:36</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/soccer/story/_/id/49073399/spain-men-world-cup-all-results-stats</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Take a look at the Spain men's national team's performance throughout the tournament's history.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Cape Verde cause another World Cup shock to deny Uruguay</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-06-22T01:55:47</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/soccer/story/_/id/49139293/cape-verde-uruguay-2026-world-cup-upset</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Cape Verde's magical start to its first World Cup isn't over. It might just be getting started.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>One of World Cup's great stories - can Cape Verde become legends?</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-06-22T01:53:23</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/c0qylwk421eo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Cape Verde continue to surprise with entertaining Uruguay draw  Cape Verde's World Cup campaign will go down in history - and they are now on the cusp</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>How Cape Verde impressed again in draw with Uruguay</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-06-22T01:02:32</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/video/clip/_/id/49139731/how-cape-verde-impressed-again-draw-uruguay</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>How Cape Verde impressed again in draw with Uruguay
+Wyndham Clark talks 'surreal' feeling of winning his second U.S. Open
+Rafael Devers visibly upse</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Cape Verde score first World Cup goals to share points with Uruguay</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-06-22T00:52:27</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/video/clip/_/id/49139607/cape-verde-score-first-world-cup-goals-share-points-uruguay</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>The first World Cup goals for Cape Verde in a 2-2 draw with Uruguay spark amazing on-field celebrations, with the African nation's chances of progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Uruguay v Cape Verde</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-06-22T00:30:13</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>http://www.espn.com/soccer/report/_/gameId/760450</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Cape Verde created fresh waves at the World Cup as they held two-time champions Uruguay to a 2-2 draw in a high-octane encounter in Miami.
+Kevin Pina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Uruguay 2-2 Cape Verde Stats: Pina Makes History as World Cup Debutants Battle to Another Draw</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-06-22T00:26:22</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/uruguay-vs-cape-verde-stats-world-cup-group-h-live/</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Cape Verde put in another brilliant display and made history on their way to a 2-2 draw against Uruguay as they sprang another sur prise at the 2026 F</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>为佛得角攻入队史世界杯首球，皮纳当选与乌拉圭一役全场最佳</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-06-22 11:31</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956730.html</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>贝尔萨：我们在某些时刻让出了比赛主导权，双方差距随之缩小</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-06-22 09:11</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956460</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026世界杯H组第二轮小组赛，乌拉圭2-2佛得角。赛后，乌拉圭主帅贝尔萨接受了DSports采访。
+关于本场比赛，贝尔萨表示：“我们未能在场上拉开实质性的差距。而当我们在一些时间段内主动让出比赛的主导权时，两队之间的实力差距也就随之被缩小了。”
+当被问及下半场巴尔韦德被安排到左路的影响时，贝尔</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>opta的H组预测：佛得角62.25%出线，乌拉圭41.2%</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-06-22 09:07</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956477</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>opta的预测显示，H组的佛得角出线概率为62.25%，乌拉圭则是41.2%。
+目前H组西班牙积4分排名第1，乌拉圭和佛得角同积2分，净胜球都是0，乌拉圭因多进1球排名第2。但由于乌拉圭最后一轮要踢西班牙，佛得角的对手则是沙特，opta更看好佛得角的出线可能。沙特虽然目前排名垫底，但和乌拉圭、佛得</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>得偿所愿，佛得角门将沃齐尼亚的母亲出现在比赛看台上</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-06-22 09:01</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956438</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>在佛得角对阵乌拉圭的比赛中，门将沃齐尼亚的母亲安娜-埃武拉出现在了球场看台上。
+本周早些时候，沃齐尼亚曾透露，母亲受签证难题和高额出行费用的困扰，无法前往现场观看自己的比赛。在世界杯首战对阵西班牙队的比赛中，沃齐尼亚表现惊艳，成为本届世界杯最受热议的球员之一。
+面对欧洲卫冕冠军西班牙队，沃齐尼亚</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>西班牙若头名出线将遇J组第二，若小组第二可能首轮碰阿根廷</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-06-22 08:38</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956424</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>美加墨世界杯小组赛两轮过后，在H组，西班牙两战积4分，乌拉圭与佛得角积2分，沙特积1分。最后一轮比赛，西班牙将与乌拉圭直接对话。
+对于H组来说，小组第一和小组第二出线后的形势可能有着天壤之别。 H1将在1/16决赛碰J2， 也就是阿根廷、奥地利所在小组的第二名，而H2将在1/16决赛碰J1，从目前</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>这场摸鱼，佛得角门将沃齐尼亚对阵乌拉圭没有完成扑救</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-06-22 08:14</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956388</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>佛得角2-2战平乌拉圭的比赛中，首轮表现亮眼的沃齐尼亚这回“美美隐身”了。
+本场比赛，乌拉圭全场只有2次射正，但都取得了进球，沃齐尼亚没能完成哪怕一次扑救。上轮对阵西班牙，沃齐尼亚7次扑救力保球门不失。
+不过今天，沃齐尼亚的队友给力，皮纳和瓦雷拉分别进球，帮助佛得角2-2战平乌拉圭。
+相关标签
+佛得</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>逼平乌拉圭！佛得角FIFA排名上升4名，来到第63位</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-06-22 08:13</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956387</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>北京时间6月22日，佛得角在H组的第二轮小组赛中2-2逼平南美豪强乌拉圭，他们的FIFA排名也来到第63位。
+在本场逼平乌拉圭后，
+佛得角的
+FIFA排名上升4名，来到第63位。而乌拉圭的
+FIFA排名下降3名，来到第19位。
+相关标签
+佛得角
+乌拉圭
+全部评论（115）
+🔥 热门
+萨蒙
+179 👍</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>黑马？！佛得角2-2平乌拉圭 皮纳斩佛得角世界杯首球穆斯莱拉送礼</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-06-22 08:04:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/match1869180date2026vnative.htm</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>西班牙足协主席：首胜正是我们所需要的，我们有实力赢世界杯</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-06-22 07:55</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956352</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>在西班牙4-0大胜沙特阿拉伯，取得本届世界杯首胜之后，身为西班牙足协主席的拉斐尔-卢赞接受了媒体的采访。
+卢赞表示：“我很享受，因为我觉得这正是我们需要的。首轮经历了小低谷之后，现在我们在享受这场重要胜利，也已经开始考虑下一场比赛。”
+谈到球队在战平佛得角后的情绪时，卢赞表示球员们“非常非常投入</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>穆斯莱拉世界杯4次失误导致丢球，有统计以来所有门将最多</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-06-22 07:48</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956354</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>北京时间6月22日，在世界杯H组第二轮乌拉圭和佛得角的比赛中，现年40岁的穆斯莱拉第61分钟出现出击失误，随后被打空门得手并且将比分追平为2-2。
+根据Opta的统计，这是穆斯莱拉职业生涯至今在世界杯上第4次因失误导致本队丢球，他也就此超越了诺伊尔、施瓦泽以及代亚耶亚(均为3次)，成为自1966年有</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>自1966年以来，乌拉圭首次世界杯半场过后逆转比分</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-06-22 07:32</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956335</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>北京时间6月22日，在世界杯H组第二轮的比赛中，马克西-阿劳霍和卡诺比奥上半时最后时刻连下两城，帮助乌拉圭在开场21分钟先丢球的情况下，半场过后2-1逆转领先于佛得角。
+根据Stats Foot的统计，马克西-阿劳霍和卡诺比奥上半时最后阶段的两粒进球也让乌拉圭队自1966年世界杯小组赛对阵法国(半场</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>生涯前两场世界杯均进球，马克西-阿劳霍成乌拉圭1954年以来首人</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-06-22 07:16</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956308</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>北京时间6月22日，在世界杯H组第二轮的比赛中，马克西-阿劳霍第44分钟打进扳平比分的关键进球，帮助乌拉圭在半场过后2-1逆转领先于佛得角。
+根据Stats Foot的统计，算上小组首轮面对沙特的进球，目前效力于葡萄牙体育的马克西-阿劳霍也就此成为自1954年的奥斯卡-明格斯以来，乌拉圭队首位在自己</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>不虚此行！新军佛得角、库拉索、约旦、乌兹均取得世界杯首球</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-06-22 06:32</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956261</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026年美加墨世界杯扩军至48支球队，佛得角、库拉索、约旦、乌兹别克斯坦成为了本届世界杯的四支新军。在佛得角队取得历史性首球后，本届世界杯的四支新军都已经取得进球，其中佛得角和库拉索还实现了拿一分的目标。
+佛得角世界杯首秀0-0逼平西班牙，就已经足够令人震惊，他们又在与乌拉圭的比赛中由凯文-皮纳</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>佛得角队史世界杯首球！皮纳超远任意球重炮，攻破乌拉圭球门！</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-06-22 06:21:00</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a3863db0eb5bnative.htm</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>40岁的穆斯莱拉第18次在世界杯登场，超卡瓦尼乌拉圭队史第一</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-06-22 06:21</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956243</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>北京时间6月22日，在世界杯H组第二轮乌拉圭与佛得角的比赛中，现年40岁的穆斯莱拉代表乌拉圭首发出场。
+根据Stats Foot的统计，这是穆斯莱拉职业生涯至今第18次代表乌拉圭在世界杯的比赛中登场，他也就此超越了前队友卡瓦尼(17场)，独占乌拉圭队史世界杯出场数第一。
+穆斯莱拉此前曾代表乌拉圭国家</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>巴埃纳：队里每个人都做好了首发准备，今天出场对我是个惊喜</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-06-22 06:08</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956194</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>西班牙4-0战胜沙特，巴埃纳赛后在FIFA混采区接受了采访。
+我觉得队里的每个人都已经做好了首发的准备。对我来说，这算是一个小小的惊喜，但同时我也认为自己已经准备好了。能够和亚马尔、奥亚萨瓦尔一起搭档锋线，感觉非常棒。奥亚萨瓦尔也是西班牙最优秀的前锋之一。总的来说，我对球队今天的表现非常满意，大家</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>西班牙在世界杯已经5次至少四球大胜，为并列第四多</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-06-22 02:08</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5955908.html</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>西班牙4-0沙特，亚马尔世界杯处子球，奥亚萨瓦尔两射一传</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-06-22 02:01</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5955874</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>北京时间6月22日世界杯小组赛第2轮，西班牙对阵沙特阿拉伯。上半场，奥亚萨瓦尔助攻，亚马尔收获个人世界杯处子球。随后，奥亚萨瓦尔在3分钟时间内完成双响。下半场，库库雷利亚射门造成坦巴蒂乌龙。全场比赛结束，西班牙4-0轻取沙特。
+第11分钟，奥亚萨瓦尔横传，亚马尔后点铲射，西班牙1-0！
+第21分</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>世界杯开场25分钟进3球，西班牙是本世纪继德国之后第二队</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:40</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5955747.html</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Lamine Yamal scores maiden World Cup goal for Spain</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-06-21T23:41:54</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/video/clip/_/id/49139145/lamine-yamal-scores-maiden-world-cup-goal-spain</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Eighteen-year-old Lamine Yamal becomes the eighth-youngest scorer in men's World Cup history in Spain's 4-0 win over Saudi Arabia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Slick Spain shine as Sharks shock the Celeste</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-06-21T22:00:00</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/matchday-11-round-up-review-highlights</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Lamine Yamal got Spain scoring at the FIFA World Cup 2026™ but it was Cabo Verde who once again stole the show with a 2-2 draw against Uruguay.
+Spain</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Uruguay vs Cape Verde Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-06-21T21:19:13</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/uruguay-vs-cape-verde-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Can Bubista’s team produce another shock in Group H at the FIFA World Cup ? We look ahead to Sunday’s clash with our Uruguay vs Cape Verde prediction </t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Spain 4-0 Saudi Arabia: World Cup Group H report</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-06-21T20:36:30</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/spain-4-0-saudi-arabia-world-cup-group-h-report</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Lamine Yamal shows why this could be his World Cup</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-06-21T19:27:01</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cj0gy46d5vro?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'He's the main man!' - Rooney on Lamine Yamal  Lamine Yamal was the story before kick-off and is dominating conversation long after the final whistle </t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Lamine Yamal Arrives at the World Cup to Play Role as Spain’s Inspiration</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>theanalyst</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:36:14</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/lamine-yamal-arrives-world-cup-stats-2026-spain</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Lamine Yamal made his first FIFA World Cup start on Sunday, and he quickly ensured Spain weren’t going to endure the same frustrations as in their hum</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Lamine Yamal Arrives at the World Cup to Play Role as Spain’s Inspiration</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:36:14</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/lamine-yamal-arrives-world-cup-stats-2026-spain/</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Lamine Yamal made his first FIFA World Cup start on Sunday, and he quickly ensured Spain weren’t going to endure the same frustrations as in their hum</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>World Cup on Fubo: Free trials, deals, offers, subscriptions, plans and more</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>goal_pw</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:22:43</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/en/news/world-cup-2026-fubo/blt5f97df30090df47f</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOAL explains how fans can stream live 2026 FIFA World Cup matches with Fubo
+The 2026 FIFA World Cup is officially underway, treating soccer fans to </t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Spain send statement with Saudi success</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:00:00</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/spain-saudi-arabia-highlights-match-report</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>This is a modal window.
+Oyarzabal and Yamal on target in dominant display as Luis de la Fuente's side showed their class with a comprehensive Group H</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Today's World Cup 2026 Kickoff Times: Complete Pacific Time (PT) Schedule</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>goal_pw</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-06-21T17:04:43</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/en/news/world-cup-2026-pacific-time-schedule/blt708391eb6f8f1517</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Pacific Time Zone
+The 2026 FIFA World Cup has completely tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Youngest goalscorers in World Cup history</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-06-21T17:00:00</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/youngest-goalscorers-all-time</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">See a ranked list of the youngest all-time goalscorers in the FIFA World Cup.
+1st) Pele – 17 years &amp; 239 days
+2nd) Manuel Rosas – 18 years &amp; 93 days
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Today's World Cup 2026 Kickoff Times: Complete Mountain Time (MT) Schedule</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>goal_pw</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-06-21T16:35:30</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/en/news/world-cup-2026-mountain-time-schedule/blt2141270bc47c494f</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Mountain Time Zone
+The 2026 FIFA World Cup has completely ta</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Today's World Cup 2026 Kickoff Times: Complete Eastern Time (ET) Schedule</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>goal_pw</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-06-21T16:11:53</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/en/news/world-cup-2026-eastern-time/blt57a4c6b10cc97d94</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Eastern Time Zone
+The 2026 FIFA World Cup has completely tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Spain vs Saudi Arabia: Group H preview, odds</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-06-21T10:00:00</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/spain-vs-saudi-arabia-group-h-preview-odds</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Spain face Saudi Arabia in Atlanta. We break down form, head‑to‑head, tactics, players to watch and decimal odds, with live tracking on Sofascore.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>The best photos from matchday 11</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-06-21T05:00:00</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/best-photos-matchday-11</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Take a look through a selection of the best photos from the FIFA World Cup 26's eleventh matchday.
+The stunning scene set prior to Spain taking on Sa</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Spain vs Saudi Arabia Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-06-21T03:50:00</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/spain-vs-saudi-arabia-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Spain will feel they have a point to prove against Saudi Arabia after a disappointing opening draw with Cape Verde at World Cup 2026. Look ahead to th</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>谁会是世界杯下一支百球球队？乌拉圭差10球，瑞典差14球</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-06-21 04:33</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5953562.html</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>The calm behind Cabo Verde's World Cup surprise</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-06-20T23:30:00</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/cabo-verde-stay-calm-spain-surprise-uruguay-test</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>After earning a historic point against Spain on their World Cup debut, Bubista's Cabo Verde have quickly shifted their focus to Uruguay.
+Many predict</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Spain vs Saudi Arabia team news and predicted XIs</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>19 hours ago</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/spain-vs-saudi-arabia-team-news-predicted-xis/</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Spain take on Saudi Arabia in a bid to get their 2026 World Cup campaign up and running with a win on Sunday at 5pm (UK time).
+La Roja were left frus</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Spain vs Saudi Arabia Bet Builder Tip: La Roja backed to recover in 12/1 punt</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>19 hours ago</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/spain-vs-saudi-arabia-bet-builder-21-06-26-world-cup/</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Spain will be desperate to respond after their surprise stalemate when they face Saudi Arabia in their second Group H game at the 2026 World Cup . Con</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Uruguay vs Cape Verde team news and predicted XIs</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>18 hours ago</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/uruguay-vs-cape-verde-team-news-predicted-xis/</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Cape Verde face another major test at the 2026 World Cup as they go from a shock opening draw with Spain straight into a meeting with Uruguay on Sunda</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Saudi Arabia World Cup 2026: Fixtures, results, manager, squad depth and tactical analysis</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>15 hours ago</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/saudi-arabia-world-cup-2026-fixtures-results-squad-analysis/</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saudi Arabia ’s 2026 World Cup campaign has been a mixed one so far, beginning with a disciplined draw against Uruguay before a heavy defeat to Spain </t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Spain World Cup 2026: Fixtures, results, manager, squad depth and tactical analysis</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>15 hours ago</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/spain-world-cup-2026-fixtures-results-squad-analysis/</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Spain ’s 2026 World Cup campaign took a sharp turn in North America as they followed up a frustrating opening draw with Cape Verde by producing a comm</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Uruguay vs Cape Verde Bet Builder: Uruguay to dominate in our 13/1 tip for tonight</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>13 hours ago</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/uruguay-vs-cape-verde-bet-builder-21-06-2026/</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Uruguay will look to bring Cape Verde ‘s impressive unbeaten start to the 2026 World Cup to an end when the two nations meet in Group H at Hard Rock S</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Uruguay vs Cape Verde; FIFA World Cup Group H</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>skysports</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>11:00pm, Sunday 21s</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://www.skysports.com/football/uruguay-vs-cape-verde/report/549805</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Uruguay                           vs Cape Verde. FIFA World Cup Group H.  11:00pm, Sunday 21st June 2026.  Hard Rock Stadium Attendance: Attendance 64</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Uruguay at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/uruguay-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>A team profile of Uruguay (La Celeste) at the FIFA World Cup 2026: 17th in the FIFA ranking, 15th appearance, two-time champions (1930, 1950), Marcelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Spain at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/spain-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>A team profile of EURO 2024 winners Spain at the FIFA World Cup 2026: 2nd in the FIFA ranking, 17th appearance, champions in 2010, Luis de la Fuente's</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Gilson Benchimol News: Lone striker in battle</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://www.rotowire.com/soccer/headlines/gilson-benchimol-news-lone-striker-in-battle-520464</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Written by RotoWire Staff
+Gilson Benchimol recorded no stats in Sunday's 2-2 draw versus Uruguay.
+Benchimol spearheaded Cape Verde's attack as the l</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Garry Rodrigues News: Starts on left wing</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://www.rotowire.com/soccer/headlines/garry-rodrigues-news-starts-on-left-wing-520462</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Written by RotoWire Staff
+Rodrigues generated one cross (one accurate) and one tackle in Sunday's 2-2 draw against Uruguay.
+Rodrigues got the start </t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Fernando Muslera News: Makes costly mistake in draw</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://www.rotowire.com/soccer/headlines/fernando-muslera-news-makes-costly-mistake-in-draw-520558</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Written by RotoWire Staff
+Muslera made two saves in Sunday's 2-2 draw with Cape Verde.
+Muslera had relatively little to do for periods of the match </t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Federico Valverde News: Game high seven shots in draw</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://www.rotowire.com/soccer/headlines/federico-valverde-news-game-high-seven-shots-in-draw-520563</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Written by RotoWire Staff
+Valverde took seven shots (zero on goal) and two crosses (zero accurate) in Sunday's 2-2 draw with Cape Verde.
+Valverde wa</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Is Lamine Yamal the youngest player to have ever scored at the World Cup?</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 16</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/person/is-lamine-yamal-the-youngest-player-to-have-ever-scored-at-the-world-cup</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Lamine Yamal bagged his first-ever World Cup goal against Saudi Arabia, making him one of the youngest scorers in the competition’s history.  Spain we</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>再见少年拉满弓，不惧岁月不惧风。亚马尔的18岁，誓要和...</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2027-06-22 14:57</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956950.html</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>罗德里、梅里诺迎来30岁生日，西班牙队晒海报为两人庆生</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-06-22 15:52:00</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a38e946eeb28native.htm</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>龙赛罗：忘了佛得角吧，亚马尔和奥亚萨瓦尔的配合堪称教科书</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-06-22 13:27</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956878.html</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>巴萨球员国家队战报：亚马尔世界杯首球，奥尔莫收获助攻</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-06-22 11:27</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956733.html</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>为什么亚马尔是西班牙进攻战术的起点，大胜沙特就是答案</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-06-22 09:51</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956532.html</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>乌拉圭2-2佛得角 ，凯文-皮纳打破僵局，埃利奥-瓦雷拉扳平比分</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-06-22 08:04</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956359</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>京时间6月22日世界杯 小组赛 第2轮，乌拉圭对阵佛得角 。乌拉圭马克西-阿劳霍破门，卡诺比奥破门。上半场，凯文-皮纳破门率先改写比分。马克西-阿劳霍补射破门扳平比分。补时阶段卡诺比奥破门将比分反超。下半场，穆斯莱拉出击失误，瓦雷拉破门将比分再度扳平。最终，乌拉圭2-2战平佛得角。
+第22分钟，凯</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>亨利：亚马尔不在时西班牙像另一支球队，其特别之处在创造力</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-06-22 07:56</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956358</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>北京时间6月22日，世界杯小组赛第2轮，西班牙4-0沙特阿拉伯。在转播节目中，亨利称赞了西班牙球员亚马尔。
+谈及亚马尔的特别之处，亨利表示：“创造力。“他是那种真正会思考比赛的球员。他总能用与众不同的方式处理比赛。他会吸引对手的注意力，并通过盘带、传球以及他自身所拥有的气场，找到别人看不到的解决办</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>朗尼克：如果亚马尔保持健康脚踏实地，他可能达到梅西的水平</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-06-22 07:41</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956344</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>奥地利队主帅朗尼克在他们对阵阿根廷的赛前新闻发布会上表示，如果亚马尔能保持健康并脚踏实地，有可能达到梅西的水平。
+在被问到世界杯淘汰赛是否可能碰上西班牙时，朗尼克表示路易斯-德拉富恩特执教的球队“不是任何人都想面对的对手”。
+“西班牙也是近年来书写足球历史的国家之一，而且他们还有拉明-亚马尔，这名未</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>波罗：亚马尔非常特别，和他并肩作战的感觉令人难以置信</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-06-22 07:40</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956340</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>西班牙在本届世界杯小组赛第二场4-0战胜沙特，波罗赛后接受了sportyTV的采访。
+是的，我觉得这是一场属于全队的精彩比赛。第一场比赛我们最需要的就是进球，但当时没能做到。这场胜利会给球队带来更多信心，因为每个人都发挥得非常出色。接下来，我们要把注意力集中到下一场比赛上。
+当然，对我们来说他是</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>TA谈葡萄牙队社媒风波：C罗全程没有任何过错，他也是受害者</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-06-22 07:35</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956318</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>根据TA的报道，2026世界杯葡萄牙战平 刚果民主共和国 后，内维斯受访称C罗只是队内普通一员，发言遭断章取义引发C罗极端粉丝网暴。其女友被造谣，C罗伴侣一度误传假消息， 无过错的C罗 也被卷入这场社交媒体谣言与网暴交织的舆论风波。
+报道称， C罗 与若昂-内维斯卷入了一场充斥着负面乱象的网络论战</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>奥尔莫：和亚马尔建立默契很容易，跟他一起踢球一直是种享受</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-06-22 06:28</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956245</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>西班牙在本届世界杯小组赛第二场4-0战胜沙特，奥尔莫赛后在FIFA混采区接受了采访。
+是的，我非常开心。我们的目标就是重新回到胜利轨道，在这届世界杯上拿到首场胜利，同时找回首场比赛中没能完全展现出来的良好感觉。我认为球队今天踢出了一场非常出色的比赛，也创造了很多机会。这一次我们把更多机会转化成了进</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>亚马尔打进世界杯首球后社媒回怼沙特球迷：我在这里</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-06-22 04:28</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956072.html</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>亚马尔：我们每个人都很出色，球队目标始终是赢下每一场比赛</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-06-22 04:14</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956043.html</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Spain 4-0 Saudi Arabia Stats: Mikel Oyarzabal and Lamine Yamal Lead First-Half Blitz</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>theanalyst</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:23:10</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/spain-vs-saudi-arabia-stats-world-cup-group-h</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>The European champions bounced back with a devastating performance to get their first win of the 2026 World Cup . Analyse the game here with our Spain</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>The Youngest Players to Score at a World Cup</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-06-21T16:18:16</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/youngest-players-to-score-world-cup-fifa/</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Who are the youngest players to score at the FIFA World Cup ? We identify the top 10, as well as some other related records.
+Pelé is the youngest pla</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>每体盘点本届世界杯U20新星：迪奥曼德、莫拉和亚马尔在列</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-06-19 18:28</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5949239.html</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>亚马尔分享沙特球迷此前唱“亚马尔在哪”歌曲并回应：我在这</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5957117&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>秀恩爱，亚马尔分享与女友用餐的合照</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5957090&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>6 days ago</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
+Get the latest World Cup Group A betting odds </t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>基本确定J组第1！阿根廷淘汰赛大概率踢H组第2，碰佛得角/沙特？</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-06-23 04:24:00</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-23/6a39953d6ee7anative.htm</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Uruguay 2-2 Cabo Verde: Araújo’s spark lights up Group H</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-06-22T02:32:18</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/uruguay-2-2-cabo-verde-araujos-spark-lights-up-group-h</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>世界杯H组 佛得角励志两连平</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-06-22 11:15</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956710.html</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>'Oh my word!' - Cape Verde take shock lead against Uruguay</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-06-21T22:46:33</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/videos/cjwg6le7193o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'Oh my word!' - Cape Verde take shock lead against Uruguay This content is not available in your location. There was an error Cape Verde's Kevin Pina </t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>'He's arrived' - Lamine Yamal scores the opener for Spain</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-06-21T16:31:27</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/videos/c1jyr87472jo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>'He's arrived' - Lamine Yamal scores the opener for Spain This content is not available in your location. There was an error Spain's Lamine Yamal scor</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Argentina vs Austria Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-06-21T09:34:56</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/argentina-vs-austria-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Can Austria stop Lionel Messi making FIFA World Cup history and securing another win for Argentina? We look ahead to the game with our Argentina vs Au</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Argentina and France among quartet eyeing knockout stage</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-06-21T09:00:00</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/preview-matchday-twelve</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Find out all the key details as Groups I and J return to action at FIFA World Cup 2026, headlined by former winners Argentina and France.
+Argentina m</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Argentina vs Austria: predictions, best bets, stats &amp; odds</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>1 hour ago</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/argentina-vs-austria-predictions-betting-tips-22-06-26/</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No previous meetings between these teams.
+No price boosts for this event.
+Bet Builder is not available yet.
+Betting markets are not available yet.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Tunisia World Cup 2026: Fixtures, results, manager, squad depth and tactical analysis</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>1 day ago</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/tunisia-world-cup-2026-fixtures-results-squad-analysis/</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Tunisia have never reached the knockout stages of the World Cup and will miss out yet again. They’ve bowed out at the group stage in each of their sev</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Saudi Arabia at the World Cup 2026: Team Guide — History, Style, Players &amp; Group H</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/saudi-arabia-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>A team profile of Saudi Arabia (Green Falcons), who beat Argentina in 2022: 61st in the FIFA ranking, 7th appearance, best result Round of 16 in 1994,</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Steven Moreira News: Three tackles in draw</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://www.rotowire.com/soccer/headlines/steven-moreira-news-three-tackles-in-draw-520463</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Written by RotoWire Staff
+Moreira had three tackles (three won), two clearances and one interception in Sunday's 2-2 draw versus Uruguay.
+Moreira go</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Diney News: Part of resilient back line</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://www.rotowire.com/soccer/headlines/diney-news-part-of-resilient-back-line-520459</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Written by RotoWire Staff
+Diney generated one shot (zero on goal) in Sunday's 2-2 draw versus Uruguay. In addition, he was given a yellow card in the</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Federico Vinas News: Kept in check by Cape Verde</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://www.rotowire.com/soccer/headlines/federico-vinas-news-kept-in-check-by-cape-verde-520559</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Written by RotoWire Staff
+Viñas recorded zero shots, won six duels, and suffered one foul in Sunday's 2-2 draw with Cape Verde.
+After firing off fiv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
